--- a/reports/telegram/aegis_daily_2026-09-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV23"/>
+  <dimension ref="A1:AV22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R2-PETRONET-IND-20260908-ba25f2</t>
+          <t>R1-ICICIBANK-IND-20260908-30fc50</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PETRONET_IND_20260908</t>
+          <t>ICICIBANK_IND_20260908</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -913,60 +913,48 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +19.4pp alpha</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #9 · Conf 35% · band STRONG · 60d left · → EXIT (rotate to GNFC.NS)</t>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↑ 2→1 · Conf 83% · momentum → · 91d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>35.4</v>
+        <v>83</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -974,93 +962,91 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
       <c r="Y3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr"/>
       <c r="AC3" s="3" t="n">
-        <v>288.1</v>
+        <v>1427.5</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>288.1</v>
+        <v>1438.5</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>285.22</v>
+        <v>1391</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>290.98</v>
+        <v>1464</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>273.69</v>
+        <v>1356.125</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>-5</v>
+        <v>-5.73</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>311.15</v>
+        <v>1503</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>8</v>
+        <v>4.48</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>331.31</v>
+        <v>1608.21</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>15</v>
+        <v>11.8</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>289.5</v>
+        <v>1423.2</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="AO3" s="3" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="AO3" s="3" t="n">
+        <v>-0.76</v>
+      </c>
       <c r="AP3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>Value · Momentum · Trend</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU3" s="3" t="n">
-        <v>19.37</v>
+        <v>4.48</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260908-30fc50</t>
+          <t>R1-SBIN-IND-20260821-686443</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260908</t>
+          <t>SBIN_IND_20260821</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1080,30 +1066,22 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>-1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
@@ -1111,12 +1089,12 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↑ 2→1 · Conf 83% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank #4 · Conf 71% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1124,11 +1102,11 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>90</v>
@@ -1136,52 +1114,52 @@
       <c r="AA4" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="n">
-        <v>1427.5</v>
+        <v>1005.9</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1438.5</v>
+        <v>1005.900024414062</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>1391</v>
+        <v>974</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1464</v>
+        <v>1037</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>1356.125</v>
+        <v>955.6049999999999</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-5.73</v>
+        <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1503</v>
+        <v>1086.372</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>4.48</v>
+        <v>8</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>1608.21</v>
+        <v>1162.41804</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>11.8</v>
+        <v>15.56</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1423.2</v>
+        <v>1016.1</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.3</v>
+        <v>-1</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="AP4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
       <c r="AS4" s="3" t="inlineStr">
         <is>
@@ -1192,23 +1170,23 @@
         <v>5</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>4.48</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-SBIN-IND-20260821-686443</t>
+          <t>R1-BEL-IND-20260908-9665b1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SBIN_IND_20260821</t>
+          <t>BEL_IND_20260908</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1228,10 +1206,14 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1240,10 +1222,14 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>-3</v>
+      </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
@@ -1251,12 +1237,12 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #4 · Conf 71% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↑ 8→5 · Conf 65% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1264,11 +1250,11 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>90</v>
@@ -1276,79 +1262,79 @@
       <c r="AA5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>1005.9</v>
+        <v>404</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1005.900024414062</v>
+        <v>388.7</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>974</v>
+        <v>392</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1037</v>
+        <v>416</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>955.6049999999999</v>
+        <v>383.8</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>-5</v>
+        <v>-1.26</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>1086.372</v>
+        <v>436.3200000000001</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>8</v>
+        <v>12.25</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>1162.41804</v>
+        <v>466.8624000000001</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>15.56</v>
+        <v>20.11</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>1016.1</v>
+        <v>405.35</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>-1</v>
+        <v>-0.33</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
+        <v>3.94</v>
+      </c>
+      <c r="AP5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="AT5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>8</v>
+        <v>12.25</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260908-9665b1</t>
+          <t>R1-ONGC-IND-20260811-f86a0f</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260908</t>
+          <t>ONGC_IND_20260811</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1368,14 +1354,10 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1384,14 +1366,10 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>-3</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
@@ -1399,12 +1377,12 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank ↑ 8→5 · Conf 65% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank #6 · Conf 68% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1412,11 +1390,11 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>90</v>
@@ -1424,79 +1402,79 @@
       <c r="AA6" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="n">
-        <v>404</v>
+        <v>233.7</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>388.7</v>
+        <v>233.6999969482422</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>392</v>
+        <v>227</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>416</v>
+        <v>241</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>383.8</v>
+        <v>222.015</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-1.26</v>
+        <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>436.3200000000001</v>
+        <v>252.396</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>12.25</v>
+        <v>8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>466.8624000000001</v>
+        <v>270.06372</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>20.11</v>
+        <v>15.56</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>405.35</v>
+        <v>234.65</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.4</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AP6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>12.25</v>
+        <v>8</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>TATASTEEL_IND_20260828</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1516,7 +1494,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1528,7 +1506,7 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -1539,12 +1517,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #6 · Conf 68% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.8%) · Rank #7 · Conf 65% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1556,7 +1534,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>90</v>
@@ -1566,77 +1544,77 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>233.7</v>
+        <v>185.6</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>233.6999969482422</v>
+        <v>185.6100006103516</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>241</v>
+        <v>191</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>222.015</v>
+        <v>176.32</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-5</v>
+        <v>-5.01</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>252.396</v>
+        <v>200.448</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>270.06372</v>
+        <v>214.47936</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>15.56</v>
+        <v>15.55</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>234.65</v>
+        <v>188.79</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-0.4</v>
+        <v>-1.68</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="AT7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
+          <t>R1-TATAPOWER-IND-20260908-1d7e13</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL_IND_20260828</t>
+          <t>TATAPOWER_IND_20260908</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1656,10 +1634,14 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1668,10 +1650,14 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
@@ -1679,12 +1665,12 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank #7 · Conf 65% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.7%) · Rank ↓ 6→9 · Conf 63% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1692,11 +1678,11 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>90</v>
@@ -1704,79 +1690,79 @@
       <c r="AA8" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>185.6</v>
+        <v>365.7</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>185.6100006103516</v>
+        <v>381.6</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>180</v>
+        <v>356</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>191</v>
+        <v>376</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>176.32</v>
+        <v>347.415</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>-5.01</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>200.448</v>
+        <v>394.956</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>7.99</v>
+        <v>3.5</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>214.47936</v>
+        <v>422.60292</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>15.55</v>
+        <v>10.75</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>188.79</v>
+        <v>368</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-1.68</v>
+        <v>-0.62</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
+        <v>-4.17</v>
+      </c>
+      <c r="AP8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR8" s="3" t="inlineStr"/>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>7.99</v>
+        <v>3.5</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-TATAPOWER-IND-20260908-1d7e13</t>
+          <t>R1-DABUR-IND-20260828-284464</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER_IND_20260908</t>
+          <t>DABUR_IND_20260828</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1796,14 +1782,10 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1812,14 +1794,10 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>3</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
@@ -1827,12 +1805,12 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↓ 6→9 · Conf 63% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank #10 · Conf 62% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1840,11 +1818,11 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>90</v>
@@ -1852,79 +1830,79 @@
       <c r="AA9" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="n">
-        <v>365.7</v>
+        <v>375.5</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>381.6</v>
+        <v>375.5</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>347.415</v>
+        <v>356.725</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>-8.960000000000001</v>
+        <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>394.956</v>
+        <v>405.54</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>422.60292</v>
+        <v>433.9278</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>10.75</v>
+        <v>15.56</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>368</v>
+        <v>380.9</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>-0.62</v>
+        <v>-1.42</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-4.17</v>
-      </c>
-      <c r="AP9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="AT9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-DABUR-IND-20260828-284464</t>
+          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>DABUR_IND_20260828</t>
+          <t>CHAMBLFERT_IND_20260804</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1939,27 +1917,35 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
+          <t>CHAMBLFERT</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Chambal Fert.</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
@@ -1967,12 +1953,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #10 · Conf 62% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>62</v>
+        <v>38.3</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -1980,91 +1966,89 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>48</v>
+        <v>22.4</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>375.5</v>
+        <v>443.35</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>375.5</v>
+        <v>443.35</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>364</v>
+        <v>438.92</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>387</v>
+        <v>447.78</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>356.725</v>
+        <v>421.1825</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>405.54</v>
+        <v>478.818</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>433.9278</v>
+        <v>509.8525</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>380.9</v>
+        <v>418.3</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>-1.42</v>
+        <v>0.18</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
       <c r="AU10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R2-PNB-IND-20260804-c7957c</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>PNB_IND_20260804</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2084,12 +2068,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Chambal Fert.</t>
+          <t>Punjab Natl. Bank</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -2100,13 +2084,13 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
@@ -2115,12 +2099,12 @@
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>38.3</v>
+        <v>32.1</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2128,7 +2112,7 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
@@ -2146,49 +2130,49 @@
         </is>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>443.35</v>
+        <v>113.36</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>443.35</v>
+        <v>113.36</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>438.92</v>
+        <v>112.23</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>447.78</v>
+        <v>114.49</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>421.1825</v>
+        <v>107.692</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>478.818</v>
+        <v>122.4288</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>509.8525</v>
+        <v>130.364</v>
       </c>
       <c r="AL11" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>418.3</v>
+        <v>117</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>0.18</v>
+        <v>-1.2</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP11" s="3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AQ11" s="3" t="n">
-        <v>0</v>
+        <v>-2.01</v>
       </c>
       <c r="AR11" s="3" t="inlineStr"/>
       <c r="AS11" s="3" t="inlineStr"/>
@@ -2198,19 +2182,19 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R2-ITC-IND-20260804-a049df</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>ITC_IND_20260804</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2230,12 +2214,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Punjab Natl. Bank</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2246,13 +2230,13 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr"/>
@@ -2261,12 +2245,12 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>32.1</v>
+        <v>38.3</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2274,7 +2258,7 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
@@ -2292,49 +2276,49 @@
         </is>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>113.36</v>
+        <v>282.9</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>113.36</v>
+        <v>282.9</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>112.23</v>
+        <v>280.07</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>114.49</v>
+        <v>285.73</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>107.692</v>
+        <v>268.7549999999999</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>122.4288</v>
+        <v>305.532</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>130.364</v>
+        <v>325.3349999999999</v>
       </c>
       <c r="AL12" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>117</v>
+        <v>264.1</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-1.2</v>
+        <v>-0.23</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AQ12" s="3" t="n">
-        <v>-2.01</v>
+        <v>0</v>
       </c>
       <c r="AR12" s="3" t="inlineStr"/>
       <c r="AS12" s="3" t="inlineStr"/>
@@ -2344,19 +2328,19 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R2-BATAINDIA-IND-20260804-21b729</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>BATAINDIA_IND_20260804</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2376,12 +2360,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Bata India</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -2392,13 +2376,13 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr"/>
@@ -2407,12 +2391,12 @@
       <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>38.3</v>
+        <v>24</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2420,7 +2404,7 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>21.6</v>
+        <v>-30.3</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
@@ -2438,49 +2422,49 @@
         </is>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>282.9</v>
+        <v>709</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>282.9</v>
+        <v>709</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>280.07</v>
+        <v>701.91</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>285.73</v>
+        <v>716.09</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>268.7549999999999</v>
+        <v>673.55</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>305.532</v>
+        <v>765.72</v>
       </c>
       <c r="AJ13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>325.3349999999999</v>
+        <v>815.3499999999999</v>
       </c>
       <c r="AL13" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>264.1</v>
+        <v>672.75</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.49</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP13" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AR13" s="3" t="inlineStr"/>
       <c r="AS13" s="3" t="inlineStr"/>
@@ -2490,19 +2474,19 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>PERSISTENT_IND_20260805</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2522,14 +2506,10 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Bata India</t>
-        </is>
-      </c>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2538,10 +2518,10 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0</v>
@@ -2553,12 +2533,12 @@
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>24</v>
+        <v>40.7</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2566,11 +2546,11 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>-30.3</v>
+        <v>23.8</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>60</v>
@@ -2580,53 +2560,53 @@
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>709</v>
+        <v>5322.4</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>709</v>
+        <v>5322.4</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>701.91</v>
+        <v>5269.18</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>716.09</v>
+        <v>5375.62</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>673.55</v>
+        <v>5056.28</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>765.72</v>
+        <v>5748.192</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>815.3499999999999</v>
+        <v>6120.759999999999</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>672.75</v>
+        <v>5643</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-0.49</v>
+        <v>-1.83</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP14" s="3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AQ14" s="3" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR14" s="3" t="inlineStr"/>
       <c r="AS14" s="3" t="inlineStr"/>
@@ -2636,19 +2616,19 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>BAJAJHLDNG_IND_20260805</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2668,7 +2648,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2680,10 +2660,10 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0</v>
@@ -2695,12 +2675,12 @@
       <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>40.7</v>
+        <v>38.3</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2708,7 +2688,7 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>23.8</v>
+        <v>20.7</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
@@ -2726,46 +2706,46 @@
         </is>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>5322.4</v>
+        <v>11127</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>5322.4</v>
+        <v>11127</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>5269.18</v>
+        <v>11015.73</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>5375.62</v>
+        <v>11238.27</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>5056.28</v>
+        <v>10570.65</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>5748.192</v>
+        <v>12017.16</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>6120.759999999999</v>
+        <v>12796.05</v>
       </c>
       <c r="AL15" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>5643</v>
+        <v>11162</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.85</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP15" s="3" t="n">
-        <v>3.32</v>
+        <v>3.69</v>
       </c>
       <c r="AQ15" s="3" t="n">
         <v>0</v>
@@ -2778,19 +2758,19 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R2-TIINDIA-IND-20260805-44fbae</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>TIINDIA_IND_20260805</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2810,7 +2790,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -2822,14 +2802,10 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr"/>
@@ -2837,12 +2813,12 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>38.3</v>
+        <v>21.5</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2850,7 +2826,7 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>20.7</v>
+        <v>-25.9</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
@@ -2868,46 +2844,46 @@
         </is>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>11127</v>
+        <v>2744.3</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>11127</v>
+        <v>2744.3</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>11015.73</v>
+        <v>2716.86</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>11238.27</v>
+        <v>2771.74</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>10570.65</v>
+        <v>2607.085</v>
       </c>
       <c r="AH16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>12017.16</v>
+        <v>2963.844000000001</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>12796.05</v>
+        <v>3155.945</v>
       </c>
       <c r="AL16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM16" s="3" t="n">
-        <v>11162</v>
+        <v>2735.4</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>-1.85</v>
+        <v>-1.37</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AQ16" s="3" t="n">
         <v>0</v>
@@ -2920,19 +2896,19 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R1-LUPIN-IND-20260908-fb05d3</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>LUPIN_IND_20260908</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2947,15 +2923,19 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2964,23 +2944,45 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-13.8%) · Rank → 3→3 · Conf 72% · momentum → · band HOLD · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.9% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="U17" s="3" t="n">
-        <v>21.5</v>
+        <v>72</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -2988,11 +2990,11 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>-25.9</v>
+        <v>71</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>60</v>
@@ -3000,55 +3002,51 @@
       <c r="AA17" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+      <c r="AB17" s="3" t="inlineStr"/>
       <c r="AC17" s="3" t="n">
-        <v>2744.3</v>
+        <v>2105</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>2744.3</v>
+        <v>2417</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>2716.86</v>
+        <v>2392.83</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>2771.74</v>
+        <v>2441.17</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>2607.085</v>
+        <v>2296.15</v>
       </c>
       <c r="AH17" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>2963.844000000001</v>
+        <v>2610.36</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>3155.945</v>
+        <v>2779.55</v>
       </c>
       <c r="AL17" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>2735.4</v>
+        <v>2110</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-1.37</v>
+        <v>-0.24</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>0</v>
+        <v>-12.91</v>
       </c>
       <c r="AP17" s="3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ17" s="3" t="n">
-        <v>0</v>
+        <v>-12.91</v>
       </c>
       <c r="AR17" s="3" t="inlineStr"/>
       <c r="AS17" s="3" t="inlineStr"/>
@@ -3058,19 +3056,19 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R1-LUPIN-IND-20260908-fb05d3</t>
+          <t>R1-PIDILITIND-IND-20260908-d60e5c</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260908</t>
+          <t>PIDILITIND_IND_20260908</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3090,12 +3088,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Lupin</t>
+          <t>Pidilite</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -3114,37 +3112,19 @@
       <c r="M18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-13.8%) · Rank → 3→3 · Conf 72% · momentum → · band HOLD · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-12.9% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3166,49 +3146,49 @@
       </c>
       <c r="AB18" s="3" t="inlineStr"/>
       <c r="AC18" s="3" t="n">
-        <v>2105</v>
+        <v>1625.5</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>2417</v>
+        <v>1625.5</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>2392.83</v>
+        <v>1609.24</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>2441.17</v>
+        <v>1641.76</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>2296.15</v>
+        <v>1544.225</v>
       </c>
       <c r="AH18" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>2610.36</v>
+        <v>1755.54</v>
       </c>
       <c r="AJ18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>2779.55</v>
+        <v>1869.325</v>
       </c>
       <c r="AL18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM18" s="3" t="n">
-        <v>2110</v>
+        <v>1629.5</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>-0.24</v>
+        <v>-3.34</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>-12.91</v>
+        <v>0</v>
       </c>
       <c r="AP18" s="3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ18" s="3" t="n">
-        <v>-12.91</v>
+        <v>0</v>
       </c>
       <c r="AR18" s="3" t="inlineStr"/>
       <c r="AS18" s="3" t="inlineStr"/>
@@ -3218,19 +3198,19 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R1-PIDILITIND-IND-20260908-d60e5c</t>
+          <t>R1-KOTAKBANK-IND-20260908-17990a</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND_IND_20260908</t>
+          <t>KOTAKBANK_IND_20260908</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3250,12 +3230,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Pidilite</t>
+          <t>Kotak Bank</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3266,10 +3246,10 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0</v>
@@ -3281,12 +3261,12 @@
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -3294,7 +3274,7 @@
         </is>
       </c>
       <c r="W19" s="3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
@@ -3308,40 +3288,40 @@
       </c>
       <c r="AB19" s="3" t="inlineStr"/>
       <c r="AC19" s="3" t="n">
-        <v>1625.5</v>
+        <v>389.3</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>1625.5</v>
+        <v>389.3</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>1609.24</v>
+        <v>385.41</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>1641.76</v>
+        <v>393.19</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>1544.225</v>
+        <v>369.835</v>
       </c>
       <c r="AH19" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>1755.54</v>
+        <v>420.444</v>
       </c>
       <c r="AJ19" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>1869.325</v>
+        <v>447.695</v>
       </c>
       <c r="AL19" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>1629.5</v>
+        <v>424.5</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>-3.34</v>
+        <v>-0.57</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>0</v>
@@ -3360,19 +3340,19 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R1-KOTAKBANK-IND-20260908-17990a</t>
+          <t>R1-IRCTC-IND-20260908-2fd378</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK_IND_20260908</t>
+          <t>IRCTC_IND_20260908</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3392,12 +3372,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Kotak Bank</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -3408,10 +3388,10 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
@@ -3423,12 +3403,12 @@
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -3436,7 +3416,7 @@
         </is>
       </c>
       <c r="W20" s="3" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="n">
@@ -3450,40 +3430,40 @@
       </c>
       <c r="AB20" s="3" t="inlineStr"/>
       <c r="AC20" s="3" t="n">
-        <v>389.3</v>
+        <v>494.35</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>389.3</v>
+        <v>494.35</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>385.41</v>
+        <v>489.41</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>393.19</v>
+        <v>499.29</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>369.835</v>
+        <v>469.6325</v>
       </c>
       <c r="AH20" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>420.444</v>
+        <v>533.898</v>
       </c>
       <c r="AJ20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>447.695</v>
+        <v>568.5024999999999</v>
       </c>
       <c r="AL20" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM20" s="3" t="n">
-        <v>424.5</v>
+        <v>474.6</v>
       </c>
       <c r="AN20" s="3" t="n">
-        <v>-0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>0</v>
@@ -3502,19 +3482,19 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260908-2fd378</t>
+          <t>R1-COALINDIA-IND-20260908-e4ec0f</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260908</t>
+          <t>COALINDIA_IND_20260908</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3534,12 +3514,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>Coal India</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3550,27 +3530,41 @@
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ+0.8%) · Rank → 10→10 · Conf 66% · momentum → · band HOLD · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -3578,7 +3572,7 @@
         </is>
       </c>
       <c r="W21" s="3" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
@@ -3592,49 +3586,49 @@
       </c>
       <c r="AB21" s="3" t="inlineStr"/>
       <c r="AC21" s="3" t="n">
-        <v>494.35</v>
+        <v>418.85</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>494.35</v>
+        <v>411.3</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>489.41</v>
+        <v>407.19</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>499.29</v>
+        <v>415.41</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>469.6325</v>
+        <v>390.735</v>
       </c>
       <c r="AH21" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>533.898</v>
+        <v>444.2040000000001</v>
       </c>
       <c r="AJ21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>568.5024999999999</v>
+        <v>472.995</v>
       </c>
       <c r="AL21" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM21" s="3" t="n">
-        <v>474.6</v>
+        <v>415.35</v>
       </c>
       <c r="AN21" s="3" t="n">
-        <v>0.31</v>
+        <v>0.84</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AP21" s="3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AQ21" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="AR21" s="3" t="inlineStr"/>
       <c r="AS21" s="3" t="inlineStr"/>
@@ -3644,19 +3638,19 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260908-e4ec0f</t>
+          <t>R1-BRITANNIA-IND-20260908-bb96d3</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260908</t>
+          <t>BRITANNIA_IND_20260908</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3676,14 +3670,10 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Coal India</t>
-        </is>
-      </c>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3692,36 +3682,22 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ+0.8%) · Rank → 10→10 · Conf 66% · momentum → · band HOLD · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
@@ -3734,7 +3710,7 @@
         </is>
       </c>
       <c r="W22" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
@@ -3748,49 +3724,49 @@
       </c>
       <c r="AB22" s="3" t="inlineStr"/>
       <c r="AC22" s="3" t="n">
-        <v>418.85</v>
+        <v>5406</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>411.3</v>
+        <v>5406</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>407.19</v>
+        <v>5351.94</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>415.41</v>
+        <v>5460.06</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>390.735</v>
+        <v>5135.7</v>
       </c>
       <c r="AH22" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>444.2040000000001</v>
+        <v>5838.48</v>
       </c>
       <c r="AJ22" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>472.995</v>
+        <v>6216.9</v>
       </c>
       <c r="AL22" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM22" s="3" t="n">
-        <v>415.35</v>
+        <v>5101.5</v>
       </c>
       <c r="AN22" s="3" t="n">
-        <v>0.84</v>
+        <v>-1.16</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AP22" s="3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AQ22" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR22" s="3" t="inlineStr"/>
       <c r="AS22" s="3" t="inlineStr"/>
@@ -3800,150 +3776,12 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 00:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>R1-BRITANNIA-IND-20260908-bb96d3</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA_IND_20260908</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T23" s="3" t="inlineStr"/>
-      <c r="U23" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="X23" s="3" t="inlineStr"/>
-      <c r="Y23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA23" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AD23" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AE23" s="3" t="n">
-        <v>5351.94</v>
-      </c>
-      <c r="AF23" s="3" t="n">
-        <v>5460.06</v>
-      </c>
-      <c r="AG23" s="3" t="n">
-        <v>5135.7</v>
-      </c>
-      <c r="AH23" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI23" s="3" t="n">
-        <v>5838.48</v>
-      </c>
-      <c r="AJ23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>6216.9</v>
-      </c>
-      <c r="AL23" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM23" s="3" t="n">
-        <v>5101.5</v>
-      </c>
-      <c r="AN23" s="3" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="AO23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08 00:54</t>
+          <t>2026-09-08 01:22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV23"/>
+  <autoFilter ref="A1:AV22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-09-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-08.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:22</t>
+          <t>2026-09-08 01:46</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-09-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-08.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 01:46</t>
+          <t>2026-09-08 03:02</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-09-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>37</v>
+        <v>35.6</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
@@ -828,46 +828,46 @@
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>597.9</v>
+        <v>591.25</v>
       </c>
       <c r="AD2" s="3" t="n">
         <v>553.3</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>591.92</v>
+        <v>585.34</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>603.88</v>
+        <v>597.16</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>562.03</v>
+        <v>555.77</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>1.58</v>
+        <v>0.45</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>669.65</v>
+        <v>662.2</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>21.03</v>
+        <v>19.68</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>741.4</v>
+        <v>733.15</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>34</v>
+        <v>32.5</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>596.7</v>
+        <v>597.9</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>0.2</v>
+        <v>-1.11</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>8.06</v>
+        <v>6.86</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>8.06</v>
+        <v>6.86</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0</v>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260908-30fc50</t>
+          <t>R2-SUNTV-IND-20260908-bf29ff</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260908</t>
+          <t>SUNTV_IND_20260908</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -913,48 +913,60 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +15.5pp alpha</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↑ 2→1 · Conf 83% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🔴 AVOID · Rank #5 · Conf 31% · band HOLD · 60d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>83</v>
+        <v>31.2</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -962,91 +974,93 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="X3" s="3" t="inlineStr"/>
+        <v>20.1</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="n">
-        <v>1427.5</v>
+        <v>454.85</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>1438.5</v>
+        <v>454.85</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1391</v>
+        <v>450.3</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>1464</v>
+        <v>459.4</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>1356.125</v>
+        <v>432.11</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>-5.73</v>
+        <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>1503</v>
+        <v>491.24</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>4.48</v>
+        <v>8</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>1608.21</v>
+        <v>523.08</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>11.8</v>
+        <v>15</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>1423.2</v>
+        <v>470.9</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AO3" s="3" t="n">
-        <v>-0.76</v>
-      </c>
+        <v>-3.41</v>
+      </c>
+      <c r="AO3" s="3" t="inlineStr"/>
       <c r="AP3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Value · Quality</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>4.48</v>
+        <v>15.48</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-SBIN-IND-20260821-686443</t>
+          <t>R1-ICICIBANK-IND-20260908-30fc50</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SBIN_IND_20260821</t>
+          <t>ICICIBANK_IND_20260908</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1066,22 +1080,30 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>-1</v>
+      </c>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
@@ -1089,12 +1111,12 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #4 · Conf 71% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↑ 2→1 · Conf 83% · momentum → · 91d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1102,11 +1124,11 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>90</v>
@@ -1114,52 +1136,52 @@
       <c r="AA4" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
+      <c r="AB4" s="3" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>1005.9</v>
+        <v>1416.3</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1005.900024414062</v>
+        <v>1438.5</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>974</v>
+        <v>1380</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1037</v>
+        <v>1452</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>955.6049999999999</v>
+        <v>1345.485</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-5</v>
+        <v>-6.47</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1086.372</v>
+        <v>1492</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>8</v>
+        <v>3.72</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>1162.41804</v>
+        <v>1596.44</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>15.56</v>
+        <v>10.98</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1016.1</v>
+        <v>1427.5</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>-1</v>
+        <v>-0.78</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
+        <v>-1.54</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR4" s="3" t="inlineStr"/>
       <c r="AS4" s="3" t="inlineStr">
         <is>
@@ -1170,23 +1192,23 @@
         <v>5</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>8</v>
+        <v>3.72</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260908-9665b1</t>
+          <t>R1-SBIN-IND-20260821-686443</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260908</t>
+          <t>SBIN_IND_20260821</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1206,14 +1228,10 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1222,14 +1240,10 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
@@ -1237,12 +1251,12 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank ↑ 8→5 · Conf 65% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank #4 · Conf 71% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1250,11 +1264,11 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>90</v>
@@ -1262,79 +1276,79 @@
       <c r="AA5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="n">
-        <v>404</v>
+        <v>1004.2</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>388.7</v>
+        <v>1004.200012207031</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>392</v>
+        <v>973</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>416</v>
+        <v>1035</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>383.8</v>
+        <v>953.99</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>-1.26</v>
+        <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>436.3200000000001</v>
+        <v>1084.536</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>12.25</v>
+        <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>466.8624000000001</v>
+        <v>1160.45352</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>20.11</v>
+        <v>15.56</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>405.35</v>
+        <v>1005.9</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AP5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="AT5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>12.25</v>
+        <v>8</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R1-BEL-IND-20260908-9665b1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>BEL_IND_20260908</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1354,10 +1368,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Bharat Electronics</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1366,10 +1384,14 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>-3</v>
+      </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
@@ -1377,12 +1399,12 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #6 · Conf 68% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.8%) · Rank ↑ 8→5 · Conf 66% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1390,11 +1412,11 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>90</v>
@@ -1402,79 +1424,79 @@
       <c r="AA6" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+      <c r="AB6" s="3" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>233.7</v>
+        <v>410</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>233.6999969482422</v>
+        <v>388.7</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>227</v>
+        <v>398</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>241</v>
+        <v>422</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>222.015</v>
+        <v>389.5</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-5</v>
+        <v>0.21</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>252.396</v>
+        <v>442.8</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>8</v>
+        <v>13.92</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>270.06372</v>
+        <v>473.796</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>15.56</v>
+        <v>21.89</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>234.65</v>
+        <v>404</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>-0.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
+        <v>5.48</v>
+      </c>
+      <c r="AP6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR6" s="3" t="inlineStr"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>8</v>
+        <v>13.92</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
+          <t>R1-ONGC-IND-20260811-f86a0f</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL_IND_20260828</t>
+          <t>ONGC_IND_20260811</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1494,7 +1516,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1506,7 +1528,7 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
@@ -1517,12 +1539,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank #7 · Conf 65% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.7%) · Rank #6 · Conf 68% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1530,11 +1552,11 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>90</v>
@@ -1544,77 +1566,77 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>185.6</v>
+        <v>233.5</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>185.6100006103516</v>
+        <v>233.4700012207031</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>176.32</v>
+        <v>221.825</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-5.01</v>
+        <v>-4.99</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>200.448</v>
+        <v>252.18</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>7.99</v>
+        <v>8.01</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>214.47936</v>
+        <v>269.8326</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>15.55</v>
+        <v>15.57</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>188.79</v>
+        <v>233.7</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-1.68</v>
+        <v>-0.1</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="AT7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>7.99</v>
+        <v>8.01</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-TATAPOWER-IND-20260908-1d7e13</t>
+          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER_IND_20260908</t>
+          <t>TATASTEEL_IND_20260828</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1634,14 +1656,10 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1650,14 +1668,10 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>3</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
@@ -1665,12 +1679,12 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↓ 6→9 · Conf 63% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.8%) · Rank #7 · Conf 65% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1678,11 +1692,11 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>90</v>
@@ -1690,79 +1704,79 @@
       <c r="AA8" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="n">
-        <v>365.7</v>
+        <v>185.6</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>381.6</v>
+        <v>185.6000061035156</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>356</v>
+        <v>180</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>376</v>
+        <v>191</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>347.415</v>
+        <v>176.32</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>-8.960000000000001</v>
+        <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>394.956</v>
+        <v>200.448</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>422.60292</v>
+        <v>214.47936</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>10.75</v>
+        <v>15.56</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>368</v>
+        <v>185.61</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.01</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-4.17</v>
-      </c>
-      <c r="AP8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-DABUR-IND-20260828-284464</t>
+          <t>R1-TATAPOWER-IND-20260908-1d7e13</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>DABUR_IND_20260828</t>
+          <t>TATAPOWER_IND_20260908</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1782,10 +1796,14 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -1794,10 +1812,14 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
@@ -1805,12 +1827,12 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #10 · Conf 62% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 6→9 · Conf 63% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1818,11 +1840,11 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>90</v>
@@ -1830,79 +1852,79 @@
       <c r="AA9" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>375.5</v>
+        <v>363.5</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>375.5</v>
+        <v>381.6</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>356.725</v>
+        <v>345.325</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>-5</v>
+        <v>-9.51</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>405.54</v>
+        <v>392.58</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>433.9278</v>
+        <v>420.0606000000001</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>15.56</v>
+        <v>10.08</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>380.9</v>
+        <v>365.7</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>-1.42</v>
+        <v>-0.6</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
+        <v>-4.74</v>
+      </c>
+      <c r="AP9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="AT9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R1-DABUR-IND-20260828-284464</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>DABUR_IND_20260828</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1917,35 +1939,27 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Chambal Fert.</t>
-        </is>
-      </c>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
@@ -1953,12 +1967,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-3.1%) · Rank #10 · Conf 62% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>38.3</v>
+        <v>62</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -1966,89 +1980,91 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>22.4</v>
+        <v>48</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>443.35</v>
+        <v>374.1</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>443.35</v>
+        <v>374.1000061035156</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>438.92</v>
+        <v>363</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>447.78</v>
+        <v>386</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>421.1825</v>
+        <v>355.395</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>478.818</v>
+        <v>404.0280000000001</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>509.8525</v>
+        <v>432.3099600000001</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>418.3</v>
+        <v>375.5</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.18</v>
+        <v>-0.37</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ10" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>CHAMBLFERT_IND_20260804</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2068,12 +2084,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Punjab Natl. Bank</t>
+          <t>Chambal Fert.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -2084,13 +2100,13 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
@@ -2099,12 +2115,12 @@
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>32.1</v>
+        <v>38.3</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2112,7 +2128,7 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
@@ -2130,49 +2146,49 @@
         </is>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>113.36</v>
+        <v>443.35</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>113.36</v>
+        <v>443.35</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>112.23</v>
+        <v>438.92</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>114.49</v>
+        <v>447.78</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>107.692</v>
+        <v>421.1825</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>122.4288</v>
+        <v>478.818</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>130.364</v>
+        <v>509.8525</v>
       </c>
       <c r="AL11" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>117</v>
+        <v>419.05</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>-1.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP11" s="3" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AQ11" s="3" t="n">
-        <v>-2.01</v>
+        <v>0</v>
       </c>
       <c r="AR11" s="3" t="inlineStr"/>
       <c r="AS11" s="3" t="inlineStr"/>
@@ -2182,19 +2198,19 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R2-PNB-IND-20260804-c7957c</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>PNB_IND_20260804</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2214,12 +2230,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Punjab Natl. Bank</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2230,13 +2246,13 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr"/>
@@ -2245,12 +2261,12 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>38.3</v>
+        <v>32.1</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2258,7 +2274,7 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
@@ -2276,49 +2292,49 @@
         </is>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>282.9</v>
+        <v>113.36</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>282.9</v>
+        <v>113.36</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>280.07</v>
+        <v>112.23</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>285.73</v>
+        <v>114.49</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>268.7549999999999</v>
+        <v>107.692</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>305.532</v>
+        <v>122.4288</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>325.3349999999999</v>
+        <v>130.364</v>
       </c>
       <c r="AL12" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>264.1</v>
+        <v>115.6</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-0.23</v>
+        <v>0.51</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="3" t="n">
-        <v>0</v>
+        <v>-2.01</v>
       </c>
       <c r="AR12" s="3" t="inlineStr"/>
       <c r="AS12" s="3" t="inlineStr"/>
@@ -2328,19 +2344,19 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R2-ITC-IND-20260804-a049df</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>ITC_IND_20260804</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2360,12 +2376,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Bata India</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -2376,13 +2392,13 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr"/>
@@ -2391,12 +2407,12 @@
       <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>24</v>
+        <v>38.3</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2404,7 +2420,7 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>-30.3</v>
+        <v>21.6</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
@@ -2422,49 +2438,49 @@
         </is>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>709</v>
+        <v>282.9</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>709</v>
+        <v>282.9</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>701.91</v>
+        <v>280.07</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>716.09</v>
+        <v>285.73</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>673.55</v>
+        <v>268.7549999999999</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>765.72</v>
+        <v>305.532</v>
       </c>
       <c r="AJ13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>815.3499999999999</v>
+        <v>325.3349999999999</v>
       </c>
       <c r="AL13" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>672.75</v>
+        <v>263.5</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.08</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP13" s="3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR13" s="3" t="inlineStr"/>
       <c r="AS13" s="3" t="inlineStr"/>
@@ -2474,19 +2490,19 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R2-BATAINDIA-IND-20260804-21b729</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>BATAINDIA_IND_20260804</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2506,10 +2522,14 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Bata India</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2518,10 +2538,10 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0</v>
@@ -2533,12 +2553,12 @@
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>40.7</v>
+        <v>24</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2546,11 +2566,11 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>23.8</v>
+        <v>-30.3</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>60</v>
@@ -2560,53 +2580,53 @@
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>5322.4</v>
+        <v>709</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>5322.4</v>
+        <v>709</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>5269.18</v>
+        <v>701.91</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>5375.62</v>
+        <v>716.09</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>5056.28</v>
+        <v>673.55</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>5748.192</v>
+        <v>765.72</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>6120.759999999999</v>
+        <v>815.3499999999999</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>5643</v>
+        <v>669.45</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-1.83</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP14" s="3" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AR14" s="3" t="inlineStr"/>
       <c r="AS14" s="3" t="inlineStr"/>
@@ -2616,19 +2636,19 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>PERSISTENT_IND_20260805</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2648,7 +2668,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2660,10 +2680,10 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>0</v>
@@ -2675,12 +2695,12 @@
       <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>38.3</v>
+        <v>40.7</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2688,7 +2708,7 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>20.7</v>
+        <v>23.8</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
@@ -2706,46 +2726,46 @@
         </is>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>11127</v>
+        <v>5322.4</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>11127</v>
+        <v>5322.4</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>11015.73</v>
+        <v>5269.18</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>11238.27</v>
+        <v>5375.62</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>10570.65</v>
+        <v>5056.28</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>12017.16</v>
+        <v>5748.192</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>12796.05</v>
+        <v>6120.759999999999</v>
       </c>
       <c r="AL15" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>11162</v>
+        <v>5540</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-1.85</v>
+        <v>-0.37</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP15" s="3" t="n">
-        <v>3.69</v>
+        <v>3.32</v>
       </c>
       <c r="AQ15" s="3" t="n">
         <v>0</v>
@@ -2758,19 +2778,19 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>BAJAJHLDNG_IND_20260805</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2790,7 +2810,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -2802,10 +2822,14 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr"/>
@@ -2813,12 +2837,12 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>21.5</v>
+        <v>38.3</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2826,7 +2850,7 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-25.9</v>
+        <v>20.7</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
@@ -2844,46 +2868,46 @@
         </is>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>2744.3</v>
+        <v>11127</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>2744.3</v>
+        <v>11127</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>2716.86</v>
+        <v>11015.73</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>2771.74</v>
+        <v>11238.27</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>2607.085</v>
+        <v>10570.65</v>
       </c>
       <c r="AH16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>2963.844000000001</v>
+        <v>12017.16</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>3155.945</v>
+        <v>12796.05</v>
       </c>
       <c r="AL16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM16" s="3" t="n">
-        <v>2735.4</v>
+        <v>10956</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>-1.37</v>
+        <v>0.45</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AQ16" s="3" t="n">
         <v>0</v>
@@ -2896,19 +2920,19 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R1-LUPIN-IND-20260908-fb05d3</t>
+          <t>R2-TIINDIA-IND-20260805-44fbae</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260908</t>
+          <t>TIINDIA_IND_20260805</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2923,19 +2947,15 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Lupin</t>
-        </is>
-      </c>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2944,45 +2964,23 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-13.8%) · Rank → 3→3 · Conf 72% · momentum → · band HOLD · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-12.9% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>72</v>
+        <v>21.5</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -2990,11 +2988,11 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>71</v>
+        <v>-25.9</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>60</v>
@@ -3002,51 +3000,55 @@
       <c r="AA17" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="n">
-        <v>2105</v>
+        <v>2744.3</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>2417</v>
+        <v>2744.3</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>2392.83</v>
+        <v>2716.86</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>2441.17</v>
+        <v>2771.74</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>2296.15</v>
+        <v>2607.085</v>
       </c>
       <c r="AH17" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>2610.36</v>
+        <v>2963.844000000001</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>2779.55</v>
+        <v>3155.945</v>
       </c>
       <c r="AL17" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>2110</v>
+        <v>2698</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-0.24</v>
+        <v>-1.62</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>-12.91</v>
+        <v>0</v>
       </c>
       <c r="AP17" s="3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ17" s="3" t="n">
-        <v>-12.91</v>
+        <v>0</v>
       </c>
       <c r="AR17" s="3" t="inlineStr"/>
       <c r="AS17" s="3" t="inlineStr"/>
@@ -3056,19 +3058,19 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R1-PIDILITIND-IND-20260908-d60e5c</t>
+          <t>R1-LUPIN-IND-20260908-fb05d3</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND_IND_20260908</t>
+          <t>LUPIN_IND_20260908</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3088,12 +3090,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Pidilite</t>
+          <t>Lupin</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -3112,19 +3114,37 @@
       <c r="M18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-13.7%) · Rank → 3→3 · Conf 72% · momentum → · band HOLD · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.9% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="U18" s="3" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3146,49 +3166,49 @@
       </c>
       <c r="AB18" s="3" t="inlineStr"/>
       <c r="AC18" s="3" t="n">
-        <v>1625.5</v>
+        <v>2106.2</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>1625.5</v>
+        <v>2417</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>1609.24</v>
+        <v>2392.83</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>1641.76</v>
+        <v>2441.17</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>1544.225</v>
+        <v>2296.15</v>
       </c>
       <c r="AH18" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>1755.54</v>
+        <v>2610.36</v>
       </c>
       <c r="AJ18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>1869.325</v>
+        <v>2779.55</v>
       </c>
       <c r="AL18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM18" s="3" t="n">
-        <v>1629.5</v>
+        <v>2105</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>-3.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>0</v>
+        <v>-12.86</v>
       </c>
       <c r="AP18" s="3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ18" s="3" t="n">
-        <v>0</v>
+        <v>-12.86</v>
       </c>
       <c r="AR18" s="3" t="inlineStr"/>
       <c r="AS18" s="3" t="inlineStr"/>
@@ -3198,19 +3218,19 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R1-KOTAKBANK-IND-20260908-17990a</t>
+          <t>R1-PIDILITIND-IND-20260908-d60e5c</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK_IND_20260908</t>
+          <t>PIDILITIND_IND_20260908</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3230,12 +3250,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Kotak Bank</t>
+          <t>Pidilite</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3246,10 +3266,10 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0</v>
@@ -3261,20 +3281,20 @@
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="n">
         <v>71</v>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>63</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
@@ -3288,40 +3308,40 @@
       </c>
       <c r="AB19" s="3" t="inlineStr"/>
       <c r="AC19" s="3" t="n">
-        <v>389.3</v>
+        <v>1625.5</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>389.3</v>
+        <v>1625.5</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>385.41</v>
+        <v>1609.24</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>393.19</v>
+        <v>1641.76</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>369.835</v>
+        <v>1544.225</v>
       </c>
       <c r="AH19" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>420.444</v>
+        <v>1755.54</v>
       </c>
       <c r="AJ19" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>447.695</v>
+        <v>1869.325</v>
       </c>
       <c r="AL19" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>424.5</v>
+        <v>1575</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>-0.57</v>
+        <v>0.37</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>0</v>
@@ -3340,19 +3360,19 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260908-2fd378</t>
+          <t>R1-KOTAKBANK-IND-20260908-17990a</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260908</t>
+          <t>KOTAKBANK_IND_20260908</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3372,12 +3392,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>Kotak Bank</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -3388,10 +3408,10 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
@@ -3403,12 +3423,12 @@
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -3416,7 +3436,7 @@
         </is>
       </c>
       <c r="W20" s="3" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="n">
@@ -3430,40 +3450,40 @@
       </c>
       <c r="AB20" s="3" t="inlineStr"/>
       <c r="AC20" s="3" t="n">
-        <v>494.35</v>
+        <v>389.3</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>494.35</v>
+        <v>389.3</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>489.41</v>
+        <v>385.41</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>499.29</v>
+        <v>393.19</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>469.6325</v>
+        <v>369.835</v>
       </c>
       <c r="AH20" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>533.898</v>
+        <v>420.444</v>
       </c>
       <c r="AJ20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>568.5024999999999</v>
+        <v>447.695</v>
       </c>
       <c r="AL20" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM20" s="3" t="n">
-        <v>474.6</v>
+        <v>422.1</v>
       </c>
       <c r="AN20" s="3" t="n">
-        <v>0.31</v>
+        <v>-0.08</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>0</v>
@@ -3482,19 +3502,19 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260908-e4ec0f</t>
+          <t>R1-IRCTC-IND-20260908-2fd378</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260908</t>
+          <t>IRCTC_IND_20260908</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3514,12 +3534,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Coal India</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3530,41 +3550,27 @@
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ+0.8%) · Rank → 10→10 · Conf 66% · momentum → · band HOLD · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -3572,7 +3578,7 @@
         </is>
       </c>
       <c r="W21" s="3" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
@@ -3586,49 +3592,49 @@
       </c>
       <c r="AB21" s="3" t="inlineStr"/>
       <c r="AC21" s="3" t="n">
-        <v>418.85</v>
+        <v>494.35</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>411.3</v>
+        <v>494.35</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>407.19</v>
+        <v>489.41</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>415.41</v>
+        <v>499.29</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>390.735</v>
+        <v>469.6325</v>
       </c>
       <c r="AH21" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>444.2040000000001</v>
+        <v>533.898</v>
       </c>
       <c r="AJ21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>472.995</v>
+        <v>568.5024999999999</v>
       </c>
       <c r="AL21" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM21" s="3" t="n">
-        <v>415.35</v>
+        <v>476.05</v>
       </c>
       <c r="AN21" s="3" t="n">
-        <v>0.84</v>
+        <v>-0.64</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AP21" s="3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AQ21" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR21" s="3" t="inlineStr"/>
       <c r="AS21" s="3" t="inlineStr"/>
@@ -3638,19 +3644,19 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R1-BRITANNIA-IND-20260908-bb96d3</t>
+          <t>R1-COALINDIA-IND-20260908-e4ec0f</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA_IND_20260908</t>
+          <t>COALINDIA_IND_20260908</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3670,10 +3676,14 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Coal India</t>
+        </is>
+      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3682,22 +3692,36 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟡 WAIT (Δ+1.4%) · Rank → 10→10 · Conf 66% · momentum → · band HOLD · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
@@ -3710,7 +3734,7 @@
         </is>
       </c>
       <c r="W22" s="3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
@@ -3724,49 +3748,49 @@
       </c>
       <c r="AB22" s="3" t="inlineStr"/>
       <c r="AC22" s="3" t="n">
-        <v>5406</v>
+        <v>421.2</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>5406</v>
+        <v>411.3</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>5351.94</v>
+        <v>407.19</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>5460.06</v>
+        <v>415.41</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>5135.7</v>
+        <v>390.735</v>
       </c>
       <c r="AH22" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>5838.48</v>
+        <v>444.2040000000001</v>
       </c>
       <c r="AJ22" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>6216.9</v>
+        <v>472.995</v>
       </c>
       <c r="AL22" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM22" s="3" t="n">
-        <v>5101.5</v>
+        <v>418.85</v>
       </c>
       <c r="AN22" s="3" t="n">
-        <v>-1.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AO22" s="3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AP22" s="3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AQ22" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="AR22" s="3" t="inlineStr"/>
       <c r="AS22" s="3" t="inlineStr"/>
@@ -3776,12 +3800,150 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 03:02</t>
+          <t>2026-09-08 04:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>R1-BRITANNIA-IND-20260908-bb96d3</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA_IND_20260908</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA23" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AC23" s="3" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AD23" s="3" t="n">
+        <v>5406</v>
+      </c>
+      <c r="AE23" s="3" t="n">
+        <v>5351.94</v>
+      </c>
+      <c r="AF23" s="3" t="n">
+        <v>5460.06</v>
+      </c>
+      <c r="AG23" s="3" t="n">
+        <v>5135.7</v>
+      </c>
+      <c r="AH23" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>5838.48</v>
+      </c>
+      <c r="AJ23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>6216.9</v>
+      </c>
+      <c r="AL23" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM23" s="3" t="n">
+        <v>5042.5</v>
+      </c>
+      <c r="AN23" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="AO23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="3" t="inlineStr"/>
+      <c r="AS23" s="3" t="inlineStr"/>
+      <c r="AT23" s="3" t="inlineStr"/>
+      <c r="AU23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:15</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV22"/>
+  <autoFilter ref="A1:AV23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-09-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV23"/>
+  <dimension ref="A1:AV26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R2-GNFC-IND-20260806-abf3d2</t>
+          <t>R1-VLO-USA-20260901-952004</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GNFC_IND_20260806</t>
+          <t>VLO_USA_20260901</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -748,23 +748,23 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>83</v>
+        <v>81.7</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,24 +783,24 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>33.3</v>
+        <v>60.6</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD→STRONG · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 62% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>34.1</v>
+        <v>62.3</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,97 +808,91 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="X2" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>68.8</v>
+      </c>
+      <c r="X2" s="3" t="inlineStr"/>
       <c r="Y2" s="3" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>591.25</v>
+        <v>370.72</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>553.3</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>585.34</v>
+        <v>367.01</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>597.16</v>
+        <v>374.43</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>555.77</v>
+        <v>352.184</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>0.45</v>
+        <v>-5</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>662.2</v>
+        <v>415.21</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>19.68</v>
+        <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>733.15</v>
+        <v>444.2747</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>32.5</v>
+        <v>19.84</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>597.9</v>
+        <v>370.69</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>-1.11</v>
+        <v>0.01</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="AP2" s="3" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="AQ2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="3" t="inlineStr">
-        <is>
-          <t>Value · Momentum · Trend</t>
-        </is>
-      </c>
-      <c r="AS2" s="3" t="inlineStr"/>
+        <v>-0</v>
+      </c>
+      <c r="AP2" s="3" t="inlineStr"/>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="AT2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R2-SUNTV-IND-20260908-bf29ff</t>
+          <t>R1-INCY-USA-20260902-658db3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SUNTV_IND_20260908</t>
+          <t>INCY_USA_20260902</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -908,40 +902,34 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +15.5pp alpha</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -949,24 +937,24 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30.5</v>
+        <v>57.6</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.8</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #5 · Conf 31% · band HOLD · 60d left · → EXIT (rotate to GNFC.NS)</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>31.2</v>
+        <v>59.4</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -974,93 +962,91 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>67.5</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
       <c r="Y3" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>454.85</v>
+        <v>126.75</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>454.85</v>
+        <v>126.75</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>450.3</v>
+        <v>125.48</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>459.4</v>
+        <v>128.02</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>432.11</v>
+        <v>120.4125</v>
       </c>
       <c r="AH3" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>491.24</v>
+        <v>141.96</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>523.08</v>
+        <v>151.8972</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>470.9</v>
+        <v>128</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>-3.41</v>
-      </c>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AO3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>Mean Reversion · Value · Quality</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU3" s="3" t="n">
-        <v>15.48</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260908-30fc50</t>
+          <t>R1-SMCI-USA-20260814-1a2943</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260908</t>
+          <t>SMCI_USA_20260814</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1070,7 +1056,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1080,43 +1066,49 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↑ 2→1 · Conf 83% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>83</v>
+        <v>59.4</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1124,11 +1116,11 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>77</v>
+        <v>55.5</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>90</v>
@@ -1136,79 +1128,79 @@
       <c r="AA4" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="n">
-        <v>1416.3</v>
+        <v>39.59</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1438.5</v>
+        <v>39.59000015258789</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>1380</v>
+        <v>39.19</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1452</v>
+        <v>39.99</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>1345.485</v>
+        <v>37.6105</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-6.47</v>
+        <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1492</v>
+        <v>44.34</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>3.72</v>
+        <v>12</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>1596.44</v>
+        <v>47.4438</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>10.98</v>
+        <v>19.84</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1427.5</v>
+        <v>37.87</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>-0.78</v>
+        <v>4.54</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="AP4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>3.72</v>
+        <v>12</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-SBIN-IND-20260821-686443</t>
+          <t>R1-SNDK-USA-20260902-6a01d7</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SBIN_IND_20260821</t>
+          <t>SNDK_USA_20260902</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1218,7 +1210,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1228,7 +1220,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1244,19 +1236,33 @@
       </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #4 · Conf 71% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 50% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>71</v>
+        <v>49.9</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1264,11 +1270,11 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>90</v>
@@ -1278,54 +1284,54 @@
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>1004.2</v>
+        <v>1740</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1004.200012207031</v>
+        <v>1740</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>973</v>
+        <v>1705.2</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1035</v>
+        <v>1774.8</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>953.99</v>
+        <v>1653</v>
       </c>
       <c r="AH5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>1084.536</v>
+        <v>1879.2</v>
       </c>
       <c r="AJ5" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>1160.45352</v>
+        <v>2010.744</v>
       </c>
       <c r="AL5" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>1005.9</v>
+        <v>1554.99</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>-0.17</v>
+        <v>11.9</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT5" s="3" t="n">
@@ -1336,19 +1342,19 @@
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260908-9665b1</t>
+          <t>R1-MU-USA-20260814-9bd573</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260908</t>
+          <t>MU_USA_20260814</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1358,7 +1364,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1368,17 +1374,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
@@ -1386,25 +1388,35 @@
       <c r="K6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank ↑ 8→5 · Conf 66% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 52% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>66</v>
+        <v>52.5</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1412,11 +1424,11 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>57</v>
+        <v>49.4</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>90</v>
@@ -1424,79 +1436,79 @@
       <c r="AA6" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="n">
-        <v>410</v>
+        <v>1016.59</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>388.7</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>398</v>
+        <v>996.26</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>422</v>
+        <v>1036.92</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>389.5</v>
+        <v>965.7605</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.21</v>
+        <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>442.8</v>
+        <v>1097.9172</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>13.92</v>
+        <v>8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>473.796</v>
+        <v>1174.771404</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>21.89</v>
+        <v>15.56</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>404</v>
+        <v>958.16</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="AP6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>13.92</v>
+        <v>8</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R1-OXY-USA-20260902-67e560</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>OXY_USA_20260902</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1506,7 +1518,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1516,13 +1528,13 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
@@ -1532,19 +1544,33 @@
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank #6 · Conf 68% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 62% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>68</v>
+        <v>62.3</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1552,11 +1578,11 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>90</v>
@@ -1566,77 +1592,77 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>233.5</v>
+        <v>60.04</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>233.4700012207031</v>
+        <v>60.04000091552734</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>227</v>
+        <v>58.84</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>240</v>
+        <v>61.24</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>221.825</v>
+        <v>57.038</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-4.99</v>
+        <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>252.18</v>
+        <v>64.84320000000001</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>269.8326</v>
+        <v>69.38222400000001</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>15.57</v>
+        <v>15.56</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>233.7</v>
+        <v>60.61</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
+          <t>R1-GRMN-USA-20260901-f19c69</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL_IND_20260828</t>
+          <t>GRMN_USA_20260901</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1646,7 +1672,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1656,13 +1682,13 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
@@ -1672,19 +1698,33 @@
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank #7 · Conf 65% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>65</v>
+        <v>59.1</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1692,11 +1732,11 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>55</v>
+        <v>48.8</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>90</v>
@@ -1706,54 +1746,54 @@
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>185.6</v>
+        <v>277.03</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>185.6000061035156</v>
+        <v>277.0299987792969</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>180</v>
+        <v>271.49</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>191</v>
+        <v>282.57</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>176.32</v>
+        <v>263.1785</v>
       </c>
       <c r="AH8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>200.448</v>
+        <v>299.1924</v>
       </c>
       <c r="AJ8" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>214.47936</v>
+        <v>320.135868</v>
       </c>
       <c r="AL8" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>185.61</v>
+        <v>277.18</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
@@ -1764,19 +1804,19 @@
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-TATAPOWER-IND-20260908-1d7e13</t>
+          <t>R1-GOOGL-USA-20260819-063f97</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER_IND_20260908</t>
+          <t>GOOGL_USA_20260819</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1786,7 +1826,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1796,43 +1836,53 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Tata Power</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 6→9 · Conf 63% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 56% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>63</v>
+        <v>55.8</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1840,11 +1890,11 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>52</v>
+        <v>45.7</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>90</v>
@@ -1852,79 +1902,79 @@
       <c r="AA9" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="n">
-        <v>363.5</v>
+        <v>338.46</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>381.6</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>354</v>
+        <v>331.69</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>373</v>
+        <v>345.23</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>345.325</v>
+        <v>321.537</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>-9.51</v>
+        <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>392.58</v>
+        <v>365.5368</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>2.88</v>
+        <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>420.0606000000001</v>
+        <v>391.124376</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>10.08</v>
+        <v>15.56</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>365.7</v>
+        <v>342.26</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>-0.6</v>
+        <v>-1.11</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-4.74</v>
-      </c>
-      <c r="AP9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AQ9" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>2.88</v>
+        <v>8</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-DABUR-IND-20260828-284464</t>
+          <t>R1-UBER-USA-20260810-2e9fcb</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>DABUR_IND_20260828</t>
+          <t>UBER_USA_20260810</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1934,7 +1984,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1944,35 +1994,49 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #10 · Conf 62% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>62</v>
+        <v>59.4</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -1980,11 +2044,11 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>48</v>
+        <v>45.7</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>90</v>
@@ -1994,44 +2058,44 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>374.1</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>374.1000061035156</v>
+        <v>75.76000213623047</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>363</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>386</v>
+        <v>77.28</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>355.395</v>
+        <v>71.97200000000001</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>404.0280000000001</v>
+        <v>81.82080000000001</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>432.3099600000001</v>
+        <v>87.54825600000001</v>
       </c>
       <c r="AL10" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>375.5</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.26</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>-0</v>
@@ -2041,7 +2105,7 @@
       <c r="AR10" s="3" t="inlineStr"/>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
@@ -2052,19 +2116,19 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R1-HOOD-USA-20260901-b01185</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>HOOD_USA_20260901</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2074,24 +2138,20 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Chambal Fert.</t>
-        </is>
-      </c>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2100,27 +2160,37 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 56% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>38.3</v>
+        <v>56.2</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2128,89 +2198,91 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.4</v>
+        <v>42.9</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>443.35</v>
+        <v>122.11</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>443.35</v>
+        <v>122.1100006103516</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>438.92</v>
+        <v>119.67</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>447.78</v>
+        <v>124.55</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>421.1825</v>
+        <v>116.0045</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>478.818</v>
+        <v>131.8788</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>509.8525</v>
+        <v>141.110316</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>419.05</v>
+        <v>124.72</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.09</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ11" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2220,7 +2292,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2230,12 +2302,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Punjab Natl. Bank</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -2246,10 +2318,10 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -2261,12 +2333,12 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>32.1</v>
+        <v>56.8</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2274,11 +2346,11 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>22.2</v>
+        <v>29.2</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>60</v>
@@ -2288,75 +2360,47 @@
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC12" s="3" t="n">
-        <v>113.36</v>
-      </c>
-      <c r="AD12" s="3" t="n">
-        <v>113.36</v>
-      </c>
-      <c r="AE12" s="3" t="n">
-        <v>112.23</v>
-      </c>
-      <c r="AF12" s="3" t="n">
-        <v>114.49</v>
-      </c>
-      <c r="AG12" s="3" t="n">
-        <v>107.692</v>
-      </c>
-      <c r="AH12" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI12" s="3" t="n">
-        <v>122.4288</v>
-      </c>
-      <c r="AJ12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK12" s="3" t="n">
-        <v>130.364</v>
-      </c>
-      <c r="AL12" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr"/>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
       <c r="AM12" s="3" t="n">
-        <v>115.6</v>
+        <v>374.34</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AO12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="3" t="n">
-        <v>-2.01</v>
-      </c>
+        <v>-1.33</v>
+      </c>
+      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr"/>
       <c r="AS12" s="3" t="inlineStr"/>
       <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU12" s="3" t="inlineStr"/>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2366,7 +2410,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2376,12 +2420,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -2392,13 +2436,13 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr"/>
@@ -2407,12 +2451,12 @@
       <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>38.3</v>
+        <v>53.6</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2420,11 +2464,11 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>21.6</v>
+        <v>27.8</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>60</v>
@@ -2434,75 +2478,47 @@
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC13" s="3" t="n">
-        <v>282.9</v>
-      </c>
-      <c r="AD13" s="3" t="n">
-        <v>282.9</v>
-      </c>
-      <c r="AE13" s="3" t="n">
-        <v>280.07</v>
-      </c>
-      <c r="AF13" s="3" t="n">
-        <v>285.73</v>
-      </c>
-      <c r="AG13" s="3" t="n">
-        <v>268.7549999999999</v>
-      </c>
-      <c r="AH13" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI13" s="3" t="n">
-        <v>305.532</v>
-      </c>
-      <c r="AJ13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK13" s="3" t="n">
-        <v>325.3349999999999</v>
-      </c>
-      <c r="AL13" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="n">
-        <v>263.5</v>
+        <v>378.75</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AO13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="3" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AQ13" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.97</v>
+      </c>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
       <c r="AS13" s="3" t="inlineStr"/>
       <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU13" s="3" t="inlineStr"/>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R2-NVDA-USA-20260908-4b1ba8</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>NVDA_USA_20260908</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2512,7 +2528,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2522,12 +2538,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Bata India</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -2538,10 +2554,10 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>0</v>
@@ -2553,12 +2569,12 @@
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 3→3 · Conf 47% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>24</v>
+        <v>47.3</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2566,11 +2582,11 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>-30.3</v>
+        <v>17.1</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>60</v>
@@ -2580,75 +2596,47 @@
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC14" s="3" t="n">
-        <v>709</v>
-      </c>
-      <c r="AD14" s="3" t="n">
-        <v>709</v>
-      </c>
-      <c r="AE14" s="3" t="n">
-        <v>701.91</v>
-      </c>
-      <c r="AF14" s="3" t="n">
-        <v>716.09</v>
-      </c>
-      <c r="AG14" s="3" t="n">
-        <v>673.55</v>
-      </c>
-      <c r="AH14" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI14" s="3" t="n">
-        <v>765.72</v>
-      </c>
-      <c r="AJ14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="3" t="n">
-        <v>815.3499999999999</v>
-      </c>
-      <c r="AL14" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="n">
-        <v>669.45</v>
+        <v>228.45</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="AO14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="3" t="n">
-        <v>-1.5</v>
-      </c>
+        <v>0.84</v>
+      </c>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
       <c r="AS14" s="3" t="inlineStr"/>
       <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU14" s="3" t="inlineStr"/>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R2-JPM-USA-20260908-d2beb6</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>JPM_USA_20260908</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2658,7 +2646,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2668,10 +2656,14 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2695,12 +2687,12 @@
       <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 4→4 · Conf 50% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>40.7</v>
+        <v>49.7</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2708,11 +2700,11 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>23.8</v>
+        <v>16.3</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>60</v>
@@ -2722,75 +2714,47 @@
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC15" s="3" t="n">
-        <v>5322.4</v>
-      </c>
-      <c r="AD15" s="3" t="n">
-        <v>5322.4</v>
-      </c>
-      <c r="AE15" s="3" t="n">
-        <v>5269.18</v>
-      </c>
-      <c r="AF15" s="3" t="n">
-        <v>5375.62</v>
-      </c>
-      <c r="AG15" s="3" t="n">
-        <v>5056.28</v>
-      </c>
-      <c r="AH15" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI15" s="3" t="n">
-        <v>5748.192</v>
-      </c>
-      <c r="AJ15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>6120.759999999999</v>
-      </c>
-      <c r="AL15" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="n">
-        <v>5540</v>
+        <v>362.06</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="AO15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AQ15" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
       <c r="AS15" s="3" t="inlineStr"/>
       <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU15" s="3" t="inlineStr"/>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R2-HON-USA-20260908-fa8c7f</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>HON_USA_20260908</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2800,7 +2764,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2810,10 +2774,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2822,10 +2790,10 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0</v>
@@ -2837,12 +2805,12 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 5→5 · Conf 50% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>38.3</v>
+        <v>50.5</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2850,11 +2818,11 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>20.7</v>
+        <v>14.8</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>60</v>
@@ -2864,75 +2832,47 @@
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" s="3" t="n">
-        <v>11127</v>
-      </c>
-      <c r="AD16" s="3" t="n">
-        <v>11127</v>
-      </c>
-      <c r="AE16" s="3" t="n">
-        <v>11015.73</v>
-      </c>
-      <c r="AF16" s="3" t="n">
-        <v>11238.27</v>
-      </c>
-      <c r="AG16" s="3" t="n">
-        <v>10570.65</v>
-      </c>
-      <c r="AH16" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI16" s="3" t="n">
-        <v>12017.16</v>
-      </c>
-      <c r="AJ16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>12796.05</v>
-      </c>
-      <c r="AL16" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="n">
-        <v>10956</v>
+        <v>207.63</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AO16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="3" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AQ16" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr"/>
       <c r="AS16" s="3" t="inlineStr"/>
       <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU16" s="3" t="inlineStr"/>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R2-GS-USA-20260908-3897c3</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>GS_USA_20260908</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2942,7 +2882,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2952,10 +2892,14 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2964,10 +2908,14 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr"/>
@@ -2975,12 +2923,12 @@
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 6→6 · Conf 51% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>21.5</v>
+        <v>51</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -2988,11 +2936,11 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>-25.9</v>
+        <v>14.5</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>60</v>
@@ -3002,75 +2950,47 @@
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC17" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AD17" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AE17" s="3" t="n">
-        <v>2716.86</v>
-      </c>
-      <c r="AF17" s="3" t="n">
-        <v>2771.74</v>
-      </c>
-      <c r="AG17" s="3" t="n">
-        <v>2607.085</v>
-      </c>
-      <c r="AH17" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI17" s="3" t="n">
-        <v>2963.844000000001</v>
-      </c>
-      <c r="AJ17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>3155.945</v>
-      </c>
-      <c r="AL17" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr"/>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr"/>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr"/>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="n">
-        <v>2698</v>
+        <v>1037.93</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="AO17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
       <c r="AS17" s="3" t="inlineStr"/>
       <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU17" s="3" t="inlineStr"/>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R1-LUPIN-IND-20260908-fb05d3</t>
+          <t>R2-AAPL-USA-20260908-b9beae</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260908</t>
+          <t>AAPL_USA_20260908</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3080,22 +3000,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Lupin</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -3106,45 +3026,27 @@
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-13.7%) · Rank → 3→3 · Conf 72% · momentum → · band HOLD · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-12.9% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
+          <t>Rank → 7→7 · Conf 50% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="n">
-        <v>72</v>
+        <v>50.5</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3152,7 +3054,7 @@
         </is>
       </c>
       <c r="W18" s="3" t="n">
-        <v>71</v>
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="inlineStr"/>
       <c r="Y18" s="3" t="n">
@@ -3164,73 +3066,49 @@
       <c r="AA18" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="n">
-        <v>2106.2</v>
-      </c>
-      <c r="AD18" s="3" t="n">
-        <v>2417</v>
-      </c>
-      <c r="AE18" s="3" t="n">
-        <v>2392.83</v>
-      </c>
-      <c r="AF18" s="3" t="n">
-        <v>2441.17</v>
-      </c>
-      <c r="AG18" s="3" t="n">
-        <v>2296.15</v>
-      </c>
-      <c r="AH18" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI18" s="3" t="n">
-        <v>2610.36</v>
-      </c>
-      <c r="AJ18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>2779.55</v>
-      </c>
-      <c r="AL18" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="n">
-        <v>2105</v>
+        <v>328.21</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AO18" s="3" t="n">
-        <v>-12.86</v>
-      </c>
-      <c r="AP18" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ18" s="3" t="n">
-        <v>-12.86</v>
-      </c>
+        <v>-2.51</v>
+      </c>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
       <c r="AS18" s="3" t="inlineStr"/>
       <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU18" s="3" t="inlineStr"/>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R1-PIDILITIND-IND-20260908-d60e5c</t>
+          <t>R2-MSFT-USA-20260908-bf7dcd</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND_IND_20260908</t>
+          <t>MSFT_USA_20260908</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3240,22 +3118,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Pidilite</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3266,10 +3144,10 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>0</v>
@@ -3281,12 +3159,12 @@
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 8→8 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
-        <v>87</v>
+        <v>53.6</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -3294,7 +3172,7 @@
         </is>
       </c>
       <c r="W19" s="3" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
@@ -3306,73 +3184,49 @@
       <c r="AA19" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="n">
-        <v>1625.5</v>
-      </c>
-      <c r="AD19" s="3" t="n">
-        <v>1625.5</v>
-      </c>
-      <c r="AE19" s="3" t="n">
-        <v>1609.24</v>
-      </c>
-      <c r="AF19" s="3" t="n">
-        <v>1641.76</v>
-      </c>
-      <c r="AG19" s="3" t="n">
-        <v>1544.225</v>
-      </c>
-      <c r="AH19" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI19" s="3" t="n">
-        <v>1755.54</v>
-      </c>
-      <c r="AJ19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>1869.325</v>
-      </c>
-      <c r="AL19" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr"/>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AF19" s="3" t="inlineStr"/>
+      <c r="AG19" s="3" t="inlineStr"/>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
       <c r="AM19" s="3" t="n">
-        <v>1575</v>
+        <v>510.12</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AO19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-2.04</v>
+      </c>
+      <c r="AO19" s="3" t="inlineStr"/>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr"/>
       <c r="AS19" s="3" t="inlineStr"/>
       <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU19" s="3" t="inlineStr"/>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R1-KOTAKBANK-IND-20260908-17990a</t>
+          <t>R2-KO-USA-20260908-391a28</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK_IND_20260908</t>
+          <t>KO_USA_20260908</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3382,22 +3236,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Kotak Bank</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -3408,10 +3262,10 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
@@ -3423,12 +3277,12 @@
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 9→9 · Conf 50% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>71</v>
+        <v>50.5</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -3436,7 +3290,7 @@
         </is>
       </c>
       <c r="W20" s="3" t="n">
-        <v>63</v>
+        <v>13.8</v>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="n">
@@ -3448,73 +3302,49 @@
       <c r="AA20" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AD20" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AE20" s="3" t="n">
-        <v>385.41</v>
-      </c>
-      <c r="AF20" s="3" t="n">
-        <v>393.19</v>
-      </c>
-      <c r="AG20" s="3" t="n">
-        <v>369.835</v>
-      </c>
-      <c r="AH20" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI20" s="3" t="n">
-        <v>420.444</v>
-      </c>
-      <c r="AJ20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>447.695</v>
-      </c>
-      <c r="AL20" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr"/>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr"/>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr"/>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="n">
-        <v>422.1</v>
+        <v>88.81</v>
       </c>
       <c r="AN20" s="3" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AO20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.83</v>
+      </c>
+      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
       <c r="AS20" s="3" t="inlineStr"/>
       <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU20" s="3" t="inlineStr"/>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260908-2fd378</t>
+          <t>R2-MMM-USA-20260908-b8fa69</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260908</t>
+          <t>MMM_USA_20260908</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3524,22 +3354,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3550,10 +3380,10 @@
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -3565,12 +3395,12 @@
       <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 7→7 · Conf 67% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 10→10 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>67</v>
+        <v>53.6</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -3578,7 +3408,7 @@
         </is>
       </c>
       <c r="W21" s="3" t="n">
-        <v>54</v>
+        <v>12.8</v>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
@@ -3590,73 +3420,49 @@
       <c r="AA21" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB21" s="3" t="inlineStr"/>
-      <c r="AC21" s="3" t="n">
-        <v>494.35</v>
-      </c>
-      <c r="AD21" s="3" t="n">
-        <v>494.35</v>
-      </c>
-      <c r="AE21" s="3" t="n">
-        <v>489.41</v>
-      </c>
-      <c r="AF21" s="3" t="n">
-        <v>499.29</v>
-      </c>
-      <c r="AG21" s="3" t="n">
-        <v>469.6325</v>
-      </c>
-      <c r="AH21" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI21" s="3" t="n">
-        <v>533.898</v>
-      </c>
-      <c r="AJ21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>568.5024999999999</v>
-      </c>
-      <c r="AL21" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr"/>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
       <c r="AM21" s="3" t="n">
-        <v>476.05</v>
+        <v>168.31</v>
       </c>
       <c r="AN21" s="3" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="AO21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr"/>
       <c r="AS21" s="3" t="inlineStr"/>
       <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU21" s="3" t="inlineStr"/>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260908-e4ec0f</t>
+          <t>R2-INTC-USA-20260908-4d7947</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260908</t>
+          <t>INTC_USA_20260908</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3666,22 +3472,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Coal India</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3692,41 +3498,27 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+      <c r="N22" s="3" t="inlineStr"/>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>🟡 WAIT (Δ+1.4%) · Rank → 10→10 · Conf 66% · momentum → · band HOLD · 61d left · → HOLD</t>
+          <t>Rank → 11→11 · Conf 29% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="n">
-        <v>66</v>
+        <v>28.7</v>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
@@ -3734,7 +3526,7 @@
         </is>
       </c>
       <c r="W22" s="3" t="n">
-        <v>50</v>
+        <v>-7.9</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
@@ -3746,73 +3538,49 @@
       <c r="AA22" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB22" s="3" t="inlineStr"/>
-      <c r="AC22" s="3" t="n">
-        <v>421.2</v>
-      </c>
-      <c r="AD22" s="3" t="n">
-        <v>411.3</v>
-      </c>
-      <c r="AE22" s="3" t="n">
-        <v>407.19</v>
-      </c>
-      <c r="AF22" s="3" t="n">
-        <v>415.41</v>
-      </c>
-      <c r="AG22" s="3" t="n">
-        <v>390.735</v>
-      </c>
-      <c r="AH22" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>444.2040000000001</v>
-      </c>
-      <c r="AJ22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>472.995</v>
-      </c>
-      <c r="AL22" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr"/>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr"/>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="n">
-        <v>418.85</v>
+        <v>91.67</v>
       </c>
       <c r="AN22" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AO22" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AP22" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AQ22" s="3" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>4.51</v>
+      </c>
+      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
       <c r="AS22" s="3" t="inlineStr"/>
       <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU22" s="3" t="inlineStr"/>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>R1-BRITANNIA-IND-20260908-bb96d3</t>
+          <t>R2-BA-USA-20260908-a3245d</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA_IND_20260908</t>
+          <t>BA_USA_20260908</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3822,20 +3590,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3844,10 +3616,10 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>0</v>
@@ -3859,12 +3631,12 @@
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 12→12 · Conf 31% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="3" t="n">
-        <v>66</v>
+        <v>30.8</v>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
@@ -3872,7 +3644,7 @@
         </is>
       </c>
       <c r="W23" s="3" t="n">
-        <v>52</v>
+        <v>-8.5</v>
       </c>
       <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
@@ -3884,66 +3656,396 @@
       <c r="AA23" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AD23" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AE23" s="3" t="n">
-        <v>5351.94</v>
-      </c>
-      <c r="AF23" s="3" t="n">
-        <v>5460.06</v>
-      </c>
-      <c r="AG23" s="3" t="n">
-        <v>5135.7</v>
-      </c>
-      <c r="AH23" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI23" s="3" t="n">
-        <v>5838.48</v>
-      </c>
-      <c r="AJ23" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>6216.9</v>
-      </c>
-      <c r="AL23" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr"/>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr"/>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr"/>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
       <c r="AM23" s="3" t="n">
-        <v>5042.5</v>
+        <v>210.51</v>
       </c>
       <c r="AN23" s="3" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="AO23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.83</v>
+      </c>
+      <c r="AO23" s="3" t="inlineStr"/>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr"/>
       <c r="AS23" s="3" t="inlineStr"/>
       <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU23" s="3" t="inlineStr"/>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 04:15</t>
+          <t>2026-09-08 08:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>R2-HD-USA-20260908-2b1b24</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>HD_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 13→13 · Conf 35% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="X24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr"/>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="n">
+        <v>318.07</v>
+      </c>
+      <c r="AN24" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr"/>
+      <c r="AS24" s="3" t="inlineStr"/>
+      <c r="AT24" s="3" t="inlineStr"/>
+      <c r="AU24" s="3" t="inlineStr"/>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 08:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>R2-DIS-USA-20260908-3fb881</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>DIS_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 14→14 · Conf 35% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="X25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr"/>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr"/>
+      <c r="AF25" s="3" t="inlineStr"/>
+      <c r="AG25" s="3" t="inlineStr"/>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr"/>
+      <c r="AM25" s="3" t="n">
+        <v>107.16</v>
+      </c>
+      <c r="AN25" s="3" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="AO25" s="3" t="inlineStr"/>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr"/>
+      <c r="AS25" s="3" t="inlineStr"/>
+      <c r="AT25" s="3" t="inlineStr"/>
+      <c r="AU25" s="3" t="inlineStr"/>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 08:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>R2-MCD-USA-20260908-320601</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>MCD_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 15→15 · Conf 28% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="X26" s="3" t="inlineStr"/>
+      <c r="Y26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr"/>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr"/>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr"/>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="3" t="n">
+        <v>259.63</v>
+      </c>
+      <c r="AN26" s="3" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AO26" s="3" t="inlineStr"/>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr"/>
+      <c r="AS26" s="3" t="inlineStr"/>
+      <c r="AT26" s="3" t="inlineStr"/>
+      <c r="AU26" s="3" t="inlineStr"/>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 08:43</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV23"/>
+  <autoFilter ref="A1:AV26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-09-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-08.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV26"/>
+  <dimension ref="A1:AV39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R1-VLO-USA-20260901-952004</t>
+          <t>R2-INCY-USA-20260908-705cfb</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>VLO_USA_20260901</t>
+          <t>INCY_USA_20260908</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -770,12 +770,12 @@
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>81.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,24 +783,24 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>60.6</v>
+        <v>57.6</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 62% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 59% · band HOLD · 17d left · → BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>62.3</v>
+        <v>59.4</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,91 +808,93 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="X2" s="3" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y2" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AB2" s="3" t="inlineStr"/>
       <c r="AC2" s="3" t="n">
-        <v>370.72</v>
+        <v>126.75</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>370.7200012207031</v>
+        <v>126.75</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>367.01</v>
+        <v>125.48</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>374.43</v>
+        <v>128.02</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>352.184</v>
+        <v>119.14</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>415.21</v>
+        <v>141.96</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>444.2747</v>
+        <v>157.17</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>19.84</v>
+        <v>24</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>370.69</v>
+        <v>128</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>0.01</v>
+        <v>-0.98</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Momentum · News</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr"/>
       <c r="AT2" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R1-INCY-USA-20260902-658db3</t>
+          <t>R2-OXY-USA-20260908-7f04e9</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>INCY_USA_20260902</t>
+          <t>OXY_USA_20260908</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -907,29 +909,29 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>78.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -937,24 +939,24 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>57.6</v>
+        <v>60.6</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #4 · Conf 62% · band HOLD · 17d left · → HOLD</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>59.4</v>
+        <v>62.3</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -962,91 +964,91 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="X3" s="3" t="inlineStr"/>
+        <v>29.1</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr"/>
       <c r="AC3" s="3" t="n">
-        <v>126.75</v>
+        <v>60.04</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>126.75</v>
+        <v>60.04</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>125.48</v>
+        <v>59.44</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>128.02</v>
+        <v>60.64</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>120.4125</v>
+        <v>57.04</v>
       </c>
       <c r="AH3" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>141.96</v>
+        <v>64.84</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>12</v>
+        <v>7.99</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>151.8972</v>
+        <v>69.05</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>19.84</v>
+        <v>15.01</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>128</v>
+        <v>60.61</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AO3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AP3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Event Driven · Value · Momentum</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>12</v>
+        <v>5.92</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-SMCI-USA-20260814-1a2943</t>
+          <t>R2-HOOD-USA-20260908-6a5b3a</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SMCI_USA_20260814</t>
+          <t>HOOD_USA_20260908</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1061,29 +1063,29 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="n">
-        <v>68.3</v>
+        <v>80.2</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
@@ -1091,24 +1093,24 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>57.6</v>
+        <v>54.5</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 56% · band STRONG · 17d left · → HOLD</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>59.4</v>
+        <v>56.2</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1116,91 +1118,91 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="X4" s="3" t="inlineStr"/>
+        <v>28.6</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="Z4" s="3" t="n">
-        <v>90</v>
-      </c>
       <c r="AA4" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AB4" s="3" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>39.59</v>
+        <v>122.11</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>39.59000015258789</v>
+        <v>122.11</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>39.19</v>
+        <v>120.89</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>39.99</v>
+        <v>123.33</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>37.6105</v>
+        <v>116</v>
       </c>
       <c r="AH4" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>44.34</v>
+        <v>131.88</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>47.4438</v>
+        <v>140.43</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>19.84</v>
+        <v>15</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>37.87</v>
+        <v>124.72</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>4.54</v>
+        <v>-2.09</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
-        <v>12</v>
+        <v>6.37</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-SNDK-USA-20260902-6a01d7</t>
+          <t>R2-UBER-USA-20260908-669f29</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SNDK_USA_20260902</t>
+          <t>UBER_USA_20260908</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1215,29 +1217,29 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>74.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
@@ -1245,24 +1247,24 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>48.1</v>
+        <v>57.6</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 50% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 59% · band HOLD · 17d left · → HOLD</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>49.9</v>
+        <v>59.4</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1270,91 +1272,91 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="X5" s="3" t="inlineStr"/>
+        <v>28.5</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>1740</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1740</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>1705.2</v>
+        <v>75</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1774.8</v>
+        <v>76.52</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>1653</v>
+        <v>71.97</v>
       </c>
       <c r="AH5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>1879.2</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AJ5" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>2010.744</v>
+        <v>87.12</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>15.56</v>
+        <v>14.99</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>1554.99</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>11.9</v>
+        <v>-0.26</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AP5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Event Driven · Growth · Quality</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>8</v>
+        <v>6.49</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-MU-USA-20260814-9bd573</t>
+          <t>R2-MU-USA-20260908-83d54f</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>MU_USA_20260814</t>
+          <t>MU_USA_20260908</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1369,7 +1371,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1386,7 +1388,7 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
@@ -1406,12 +1408,12 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 52% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #7 · Conf 52% · band HOLD · 9d left · → HOLD</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
@@ -1424,52 +1426,50 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="X6" s="3" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AB6" s="3" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
         <v>1016.59</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>1016.590026855469</v>
+        <v>1016.59</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>996.26</v>
+        <v>1006.42</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>1036.92</v>
+        <v>1026.76</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>965.7605</v>
+        <v>965.76</v>
       </c>
       <c r="AH6" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>1097.9172</v>
+        <v>1097.92</v>
       </c>
       <c r="AJ6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>1174.771404</v>
+        <v>1169.08</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM6" s="3" t="n">
         <v>958.16</v>
@@ -1478,37 +1478,39 @@
         <v>6.1</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Growth · Quality · Momentum</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
       <c r="AU6" s="3" t="n">
-        <v>8</v>
+        <v>7.03</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-OXY-USA-20260902-67e560</t>
+          <t>R2-SNDK-USA-20260908-6245dc</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>OXY_USA_20260902</t>
+          <t>SNDK_USA_20260908</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1523,12 +1525,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1540,12 +1542,12 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -1553,24 +1555,24 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>60.6</v>
+        <v>48.1</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 62% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #8 · Conf 50% · band HOLD · 9d left · → HOLD</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>62.3</v>
+        <v>49.9</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1578,91 +1580,91 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="X7" s="3" t="inlineStr"/>
+        <v>26.4</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y7" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>60.04</v>
+        <v>1740</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>60.04000091552734</v>
+        <v>1740</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>58.84</v>
+        <v>1722.6</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>61.24</v>
+        <v>1757.4</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>57.038</v>
+        <v>1653</v>
       </c>
       <c r="AH7" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>64.84320000000001</v>
+        <v>1879.2</v>
       </c>
       <c r="AJ7" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>69.38222400000001</v>
+        <v>2001</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>60.61</v>
+        <v>1554.99</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>11.9</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Momentum</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-GRMN-USA-20260901-f19c69</t>
+          <t>R2-GRMN-USA-20260908-8a1473</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>GRMN_USA_20260901</t>
+          <t>GRMN_USA_20260908</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1677,7 +1679,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1694,7 +1696,7 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
@@ -1714,12 +1716,12 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 59% · band HOLD · 17d left · → HOLD</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
@@ -1732,52 +1734,50 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="X8" s="3" t="inlineStr"/>
+        <v>26.4</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
         <v>277.03</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>277.0299987792969</v>
+        <v>277.03</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>271.49</v>
+        <v>274.26</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>282.57</v>
+        <v>279.8</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>263.1785</v>
+        <v>263.18</v>
       </c>
       <c r="AH8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>299.1924</v>
+        <v>299.19</v>
       </c>
       <c r="AJ8" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>320.135868</v>
+        <v>318.58</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM8" s="3" t="n">
         <v>277.18</v>
@@ -1788,35 +1788,37 @@
       <c r="AO8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AP8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Quality · News</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
       <c r="AU8" s="3" t="n">
-        <v>8</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-GOOGL-USA-20260819-063f97</t>
+          <t>R2-GOOGL-USA-20260908-8bd1f2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>GOOGL_USA_20260819</t>
+          <t>GOOGL_USA_20260908</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1831,7 +1833,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1852,7 +1854,7 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
@@ -1872,12 +1874,12 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 56% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #10 · Conf 56% · band HOLD · 9d left · → HOLD</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
@@ -1890,52 +1892,50 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="X9" s="3" t="inlineStr"/>
+        <v>25.5</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AA9" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
         <v>338.46</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>338.4599914550781</v>
+        <v>338.46</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>331.69</v>
+        <v>335.08</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>345.23</v>
+        <v>341.84</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>321.537</v>
+        <v>321.54</v>
       </c>
       <c r="AH9" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>365.5368</v>
+        <v>365.54</v>
       </c>
       <c r="AJ9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>391.124376</v>
+        <v>389.23</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM9" s="3" t="n">
         <v>342.26</v>
@@ -1946,35 +1946,37 @@
       <c r="AO9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AP9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Growth · Event Driven · Quality</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="n">
-        <v>8</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-UBER-USA-20260810-2e9fcb</t>
+          <t>R2-PKG-USA-20260908-527990</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UBER_USA_20260810</t>
+          <t>PKG_USA_20260908</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1989,12 +1991,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -2006,37 +2008,37 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>52.8</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>57.6</v>
+        <v>32.6</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #11 · Conf 34% · band EXIT · 9d left · → HOLD</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>59.4</v>
+        <v>34.4</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2044,91 +2046,91 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="X10" s="3" t="inlineStr"/>
+        <v>-26.3</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AB10" s="3" t="inlineStr"/>
       <c r="AC10" s="3" t="n">
-        <v>75.76000000000001</v>
+        <v>237.25</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>75.76000213623047</v>
+        <v>237.25</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>74.23999999999999</v>
+        <v>234.88</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>77.28</v>
+        <v>239.62</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>71.97200000000001</v>
+        <v>225.39</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>81.82080000000001</v>
+        <v>256.23</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>87.54825600000001</v>
+        <v>272.84</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>75.95999999999999</v>
+        <v>234.57</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>-0.26</v>
+        <v>1.14</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
       <c r="AU10" s="3" t="n">
-        <v>8</v>
+        <v>61.27</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-HOOD-USA-20260901-b01185</t>
+          <t>R2-CHD-USA-20260908-22c8d5</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>HOOD_USA_20260901</t>
+          <t>CHD_USA_20260908</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2143,12 +2145,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -2160,37 +2162,37 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>80.2</v>
+        <v>52.9</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>54.5</v>
+        <v>34.3</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-1.8</v>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 34.8% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 56% · momentum → · band STRONG · 91d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #12 · Conf 36% · band EXIT · 9d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>56.2</v>
+        <v>36.1</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2198,91 +2200,91 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="X11" s="3" t="inlineStr"/>
+        <v>-27.6</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="n">
-        <v>122.11</v>
+        <v>98.55</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>122.1100006103516</v>
+        <v>98.55</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>119.67</v>
+        <v>97.56</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>124.55</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>116.0045</v>
+        <v>93.62</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>131.8788</v>
+        <v>106.43</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>141.110316</v>
+        <v>113.33</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>15.56</v>
+        <v>15</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>124.72</v>
+        <v>98.59</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>-2.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr"/>
+      <c r="AT11" s="3" t="inlineStr"/>
       <c r="AU11" s="3" t="n">
-        <v>8</v>
+        <v>62.63</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R2-TRV-USA-20260810-a2c57b</t>
+          <t>R2-J-USA-20260908-3434cf</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TRV_USA_20260810</t>
+          <t>J_USA_20260908</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2302,43 +2304,55 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>→ SMCI · +62.7pp alpha</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #13 · Conf 36% · band EXIT · 9d left · → EXIT (rotate to SMCI)</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>56.8</v>
+        <v>36.1</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2346,61 +2360,89 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="X12" s="3" t="inlineStr"/>
+        <v>-27.7</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AC12" s="3" t="inlineStr"/>
-      <c r="AD12" s="3" t="inlineStr"/>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AC12" s="3" t="n">
+        <v>146.23</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>146.23</v>
+      </c>
+      <c r="AE12" s="3" t="n">
+        <v>144.77</v>
+      </c>
+      <c r="AF12" s="3" t="n">
+        <v>147.69</v>
+      </c>
+      <c r="AG12" s="3" t="n">
+        <v>138.92</v>
+      </c>
+      <c r="AH12" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="AJ12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>168.16</v>
+      </c>
+      <c r="AL12" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AM12" s="3" t="n">
-        <v>374.34</v>
+        <v>147.54</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.89</v>
       </c>
       <c r="AO12" s="3" t="inlineStr"/>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AP12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
       <c r="AS12" s="3" t="inlineStr"/>
       <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="n">
+        <v>62.69</v>
+      </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R2-V-USA-20260810-1697f4</t>
+          <t>R2-ESS-USA-20260908-9aed30</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>V_USA_20260810</t>
+          <t>ESS_USA_20260908</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2420,43 +2462,55 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
+          <t>ESS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>→ SMCI · +63.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #14 · Conf 34% · band EXIT · 9d left · → EXIT (rotate to SMCI)</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>53.6</v>
+        <v>34.4</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2464,61 +2518,89 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="X13" s="3" t="inlineStr"/>
+        <v>-28.6</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y13" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AC13" s="3" t="inlineStr"/>
-      <c r="AD13" s="3" t="inlineStr"/>
-      <c r="AE13" s="3" t="inlineStr"/>
-      <c r="AF13" s="3" t="inlineStr"/>
-      <c r="AG13" s="3" t="inlineStr"/>
-      <c r="AH13" s="3" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="n">
+        <v>278.61</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>278.61</v>
+      </c>
+      <c r="AE13" s="3" t="n">
+        <v>275.82</v>
+      </c>
+      <c r="AF13" s="3" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="AG13" s="3" t="n">
+        <v>264.68</v>
+      </c>
+      <c r="AH13" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI13" s="3" t="n">
+        <v>300.9</v>
+      </c>
+      <c r="AJ13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>320.4</v>
+      </c>
+      <c r="AL13" s="3" t="n">
+        <v>15</v>
+      </c>
       <c r="AM13" s="3" t="n">
-        <v>378.75</v>
+        <v>278.65</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.01</v>
       </c>
       <c r="AO13" s="3" t="inlineStr"/>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
       <c r="AS13" s="3" t="inlineStr"/>
       <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AU13" s="3" t="n">
+        <v>63.63</v>
+      </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R2-NVDA-USA-20260908-4b1ba8</t>
+          <t>R2-SW-USA-20260908-aaa712</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>NVDA_USA_20260908</t>
+          <t>SW_USA_20260908</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2538,43 +2620,55 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>→ SMCI · +66.7pp alpha</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>Rank → 3→3 · Conf 47% · momentum → · 61d left · → HOLD</t>
+          <t>🔴 AVOID · Rank #15 · Conf 32% · band EXIT · 9d left · → EXIT (rotate to SMCI)</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>47.3</v>
+        <v>32.3</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2582,61 +2676,89 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X14" s="3" t="inlineStr"/>
+        <v>-31.7</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC14" s="3" t="inlineStr"/>
-      <c r="AD14" s="3" t="inlineStr"/>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="AE14" s="3" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="AF14" s="3" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="AG14" s="3" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="AH14" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI14" s="3" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AJ14" s="3" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="AL14" s="3" t="n">
+        <v>14.99</v>
+      </c>
       <c r="AM14" s="3" t="n">
-        <v>228.45</v>
+        <v>45.26</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>0.84</v>
+        <v>1.26</v>
       </c>
       <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
+        </is>
+      </c>
       <c r="AS14" s="3" t="inlineStr"/>
       <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
+      <c r="AU14" s="3" t="n">
+        <v>66.70999999999999</v>
+      </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-JPM-USA-20260908-d2beb6</t>
+          <t>R1-VLO-USA-20260908-bc2705</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>JPM_USA_20260908</t>
+          <t>VLO_USA_20260908</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2651,48 +2773,54 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase</t>
-        </is>
-      </c>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>Rank → 4→4 · Conf 50% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 62% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>49.7</v>
+        <v>62.3</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2700,61 +2828,91 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.3</v>
+        <v>68.8</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC15" s="3" t="inlineStr"/>
-      <c r="AD15" s="3" t="inlineStr"/>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="n">
+        <v>370.72</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>370.72</v>
+      </c>
+      <c r="AE15" s="3" t="n">
+        <v>367.01</v>
+      </c>
+      <c r="AF15" s="3" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="AG15" s="3" t="n">
+        <v>352.184</v>
+      </c>
+      <c r="AH15" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>415.21</v>
+      </c>
+      <c r="AJ15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>444.2747</v>
+      </c>
+      <c r="AL15" s="3" t="n">
+        <v>19.84</v>
+      </c>
       <c r="AM15" s="3" t="n">
-        <v>362.06</v>
+        <v>370.69</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="AO15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-HON-USA-20260908-fa8c7f</t>
+          <t>R1-INCY-USA-20260908-c42aa4</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>HON_USA_20260908</t>
+          <t>INCY_USA_20260908</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2769,48 +2927,54 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
+          <t>INCY</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="3" t="inlineStr"/>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>Rank → 5→5 · Conf 50% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>50.5</v>
+        <v>59.4</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2818,61 +2982,91 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>14.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA16" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC16" s="3" t="inlineStr"/>
-      <c r="AD16" s="3" t="inlineStr"/>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="AE16" s="3" t="n">
+        <v>125.48</v>
+      </c>
+      <c r="AF16" s="3" t="n">
+        <v>128.02</v>
+      </c>
+      <c r="AG16" s="3" t="n">
+        <v>120.4125</v>
+      </c>
+      <c r="AH16" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>141.96</v>
+      </c>
+      <c r="AJ16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>151.8972</v>
+      </c>
+      <c r="AL16" s="3" t="n">
+        <v>19.84</v>
+      </c>
       <c r="AM16" s="3" t="n">
-        <v>207.63</v>
+        <v>128</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
+        <v>-0.98</v>
+      </c>
+      <c r="AO16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-GS-USA-20260908-3897c3</t>
+          <t>R1-SMCI-USA-20260908-c8a03d</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GS_USA_20260908</t>
+          <t>SMCI_USA_20260908</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2887,48 +3081,54 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>Rank → 6→6 · Conf 51% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 59% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>51</v>
+        <v>59.4</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -2936,61 +3136,91 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>14.5</v>
+        <v>55.5</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA17" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC17" s="3" t="inlineStr"/>
-      <c r="AD17" s="3" t="inlineStr"/>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AC17" s="3" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="AE17" s="3" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="AF17" s="3" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="AG17" s="3" t="n">
+        <v>37.6105</v>
+      </c>
+      <c r="AH17" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="AJ17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>47.4438</v>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>19.84</v>
+      </c>
       <c r="AM17" s="3" t="n">
-        <v>1037.93</v>
+        <v>37.87</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
+        <v>4.54</v>
+      </c>
+      <c r="AO17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU17" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R2-AAPL-USA-20260908-b9beae</t>
+          <t>R1-SNDK-USA-20260908-100b74</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>AAPL_USA_20260908</t>
+          <t>SNDK_USA_20260908</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3005,48 +3235,54 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>Rank → 7→7 · Conf 50% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 50% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3054,61 +3290,91 @@
         </is>
       </c>
       <c r="W18" s="3" t="n">
-        <v>14.4</v>
+        <v>51</v>
       </c>
       <c r="X18" s="3" t="inlineStr"/>
       <c r="Y18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC18" s="3" t="inlineStr"/>
-      <c r="AD18" s="3" t="inlineStr"/>
-      <c r="AE18" s="3" t="inlineStr"/>
-      <c r="AF18" s="3" t="inlineStr"/>
-      <c r="AG18" s="3" t="inlineStr"/>
-      <c r="AH18" s="3" t="inlineStr"/>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AC18" s="3" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AD18" s="3" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AE18" s="3" t="n">
+        <v>1705.2</v>
+      </c>
+      <c r="AF18" s="3" t="n">
+        <v>1774.8</v>
+      </c>
+      <c r="AG18" s="3" t="n">
+        <v>1653</v>
+      </c>
+      <c r="AH18" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI18" s="3" t="n">
+        <v>1879.2</v>
+      </c>
+      <c r="AJ18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>2010.744</v>
+      </c>
+      <c r="AL18" s="3" t="n">
+        <v>15.56</v>
+      </c>
       <c r="AM18" s="3" t="n">
-        <v>328.21</v>
+        <v>1554.99</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="AO18" s="3" t="inlineStr"/>
-      <c r="AP18" s="3" t="inlineStr"/>
-      <c r="AQ18" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="AO18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr"/>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU18" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R2-MSFT-USA-20260908-bf7dcd</t>
+          <t>R1-MU-USA-20260908-2c042f</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MSFT_USA_20260908</t>
+          <t>MU_USA_20260908</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3123,19 +3389,15 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3144,27 +3406,37 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>Rank → 8→8 · Conf 54% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 52% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
-        <v>53.6</v>
+        <v>52.5</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -3172,61 +3444,91 @@
         </is>
       </c>
       <c r="W19" s="3" t="n">
-        <v>14</v>
+        <v>49.4</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC19" s="3" t="inlineStr"/>
-      <c r="AD19" s="3" t="inlineStr"/>
-      <c r="AE19" s="3" t="inlineStr"/>
-      <c r="AF19" s="3" t="inlineStr"/>
-      <c r="AG19" s="3" t="inlineStr"/>
-      <c r="AH19" s="3" t="inlineStr"/>
-      <c r="AI19" s="3" t="inlineStr"/>
-      <c r="AJ19" s="3" t="inlineStr"/>
-      <c r="AK19" s="3" t="inlineStr"/>
-      <c r="AL19" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB19" s="3" t="inlineStr"/>
+      <c r="AC19" s="3" t="n">
+        <v>1016.59</v>
+      </c>
+      <c r="AD19" s="3" t="n">
+        <v>1016.59</v>
+      </c>
+      <c r="AE19" s="3" t="n">
+        <v>996.26</v>
+      </c>
+      <c r="AF19" s="3" t="n">
+        <v>1036.92</v>
+      </c>
+      <c r="AG19" s="3" t="n">
+        <v>965.7605</v>
+      </c>
+      <c r="AH19" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI19" s="3" t="n">
+        <v>1097.9172</v>
+      </c>
+      <c r="AJ19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>1174.771404</v>
+      </c>
+      <c r="AL19" s="3" t="n">
+        <v>15.56</v>
+      </c>
       <c r="AM19" s="3" t="n">
-        <v>510.12</v>
+        <v>958.16</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="AO19" s="3" t="inlineStr"/>
-      <c r="AP19" s="3" t="inlineStr"/>
-      <c r="AQ19" s="3" t="inlineStr"/>
+        <v>6.1</v>
+      </c>
+      <c r="AO19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU19" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R2-KO-USA-20260908-391a28</t>
+          <t>R1-OXY-USA-20260908-ae3ffa</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>KO_USA_20260908</t>
+          <t>OXY_USA_20260908</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3241,19 +3543,15 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Coca-Cola</t>
-        </is>
-      </c>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3262,27 +3560,37 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="3" t="inlineStr"/>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>Rank → 9→9 · Conf 50% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 62% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>50.5</v>
+        <v>62.3</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -3290,61 +3598,91 @@
         </is>
       </c>
       <c r="W20" s="3" t="n">
-        <v>13.8</v>
+        <v>49</v>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC20" s="3" t="inlineStr"/>
-      <c r="AD20" s="3" t="inlineStr"/>
-      <c r="AE20" s="3" t="inlineStr"/>
-      <c r="AF20" s="3" t="inlineStr"/>
-      <c r="AG20" s="3" t="inlineStr"/>
-      <c r="AH20" s="3" t="inlineStr"/>
-      <c r="AI20" s="3" t="inlineStr"/>
-      <c r="AJ20" s="3" t="inlineStr"/>
-      <c r="AK20" s="3" t="inlineStr"/>
-      <c r="AL20" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AC20" s="3" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="AD20" s="3" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="AE20" s="3" t="n">
+        <v>58.84</v>
+      </c>
+      <c r="AF20" s="3" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="AG20" s="3" t="n">
+        <v>57.038</v>
+      </c>
+      <c r="AH20" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI20" s="3" t="n">
+        <v>64.84320000000001</v>
+      </c>
+      <c r="AJ20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>69.38222400000001</v>
+      </c>
+      <c r="AL20" s="3" t="n">
+        <v>15.56</v>
+      </c>
       <c r="AM20" s="3" t="n">
-        <v>88.81</v>
+        <v>60.61</v>
       </c>
       <c r="AN20" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="AO20" s="3" t="inlineStr"/>
-      <c r="AP20" s="3" t="inlineStr"/>
-      <c r="AQ20" s="3" t="inlineStr"/>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AO20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="inlineStr"/>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU20" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R2-MMM-USA-20260908-b8fa69</t>
+          <t>R1-GRMN-USA-20260908-cc92a5</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MMM_USA_20260908</t>
+          <t>GRMN_USA_20260908</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3359,19 +3697,15 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>MMM</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3380,27 +3714,37 @@
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>Rank → 10→10 · Conf 54% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>53.6</v>
+        <v>59.1</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -3408,61 +3752,91 @@
         </is>
       </c>
       <c r="W21" s="3" t="n">
-        <v>12.8</v>
+        <v>48.9</v>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC21" s="3" t="inlineStr"/>
-      <c r="AD21" s="3" t="inlineStr"/>
-      <c r="AE21" s="3" t="inlineStr"/>
-      <c r="AF21" s="3" t="inlineStr"/>
-      <c r="AG21" s="3" t="inlineStr"/>
-      <c r="AH21" s="3" t="inlineStr"/>
-      <c r="AI21" s="3" t="inlineStr"/>
-      <c r="AJ21" s="3" t="inlineStr"/>
-      <c r="AK21" s="3" t="inlineStr"/>
-      <c r="AL21" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AC21" s="3" t="n">
+        <v>277.03</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>277.03</v>
+      </c>
+      <c r="AE21" s="3" t="n">
+        <v>271.49</v>
+      </c>
+      <c r="AF21" s="3" t="n">
+        <v>282.57</v>
+      </c>
+      <c r="AG21" s="3" t="n">
+        <v>263.1785</v>
+      </c>
+      <c r="AH21" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI21" s="3" t="n">
+        <v>299.1924</v>
+      </c>
+      <c r="AJ21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>320.135868</v>
+      </c>
+      <c r="AL21" s="3" t="n">
+        <v>15.56</v>
+      </c>
       <c r="AM21" s="3" t="n">
-        <v>168.31</v>
+        <v>277.18</v>
       </c>
       <c r="AN21" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AO21" s="3" t="inlineStr"/>
-      <c r="AP21" s="3" t="inlineStr"/>
-      <c r="AQ21" s="3" t="inlineStr"/>
+        <v>-0.05</v>
+      </c>
+      <c r="AO21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU21" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R2-INTC-USA-20260908-4d7947</t>
+          <t>R1-GOOGL-USA-20260908-360496</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>INTC_USA_20260908</t>
+          <t>GOOGL_USA_20260908</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3477,17 +3851,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3498,27 +3872,37 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>Rank → 11→11 · Conf 29% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 56% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="n">
-        <v>28.7</v>
+        <v>55.8</v>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
@@ -3526,61 +3910,91 @@
         </is>
       </c>
       <c r="W22" s="3" t="n">
-        <v>-7.9</v>
+        <v>45.7</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC22" s="3" t="inlineStr"/>
-      <c r="AD22" s="3" t="inlineStr"/>
-      <c r="AE22" s="3" t="inlineStr"/>
-      <c r="AF22" s="3" t="inlineStr"/>
-      <c r="AG22" s="3" t="inlineStr"/>
-      <c r="AH22" s="3" t="inlineStr"/>
-      <c r="AI22" s="3" t="inlineStr"/>
-      <c r="AJ22" s="3" t="inlineStr"/>
-      <c r="AK22" s="3" t="inlineStr"/>
-      <c r="AL22" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AC22" s="3" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="AD22" s="3" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="AE22" s="3" t="n">
+        <v>331.69</v>
+      </c>
+      <c r="AF22" s="3" t="n">
+        <v>345.23</v>
+      </c>
+      <c r="AG22" s="3" t="n">
+        <v>321.537</v>
+      </c>
+      <c r="AH22" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI22" s="3" t="n">
+        <v>365.5368</v>
+      </c>
+      <c r="AJ22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>391.124376</v>
+      </c>
+      <c r="AL22" s="3" t="n">
+        <v>15.56</v>
+      </c>
       <c r="AM22" s="3" t="n">
-        <v>91.67</v>
+        <v>342.26</v>
       </c>
       <c r="AN22" s="3" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="AO22" s="3" t="inlineStr"/>
-      <c r="AP22" s="3" t="inlineStr"/>
-      <c r="AQ22" s="3" t="inlineStr"/>
+        <v>-1.11</v>
+      </c>
+      <c r="AO22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="inlineStr"/>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU22" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>R2-BA-USA-20260908-a3245d</t>
+          <t>R1-UBER-USA-20260908-269e02</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BA_USA_20260908</t>
+          <t>UBER_USA_20260908</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3595,19 +4009,15 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3616,27 +4026,37 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>Rank → 12→12 · Conf 31% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 59% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="3" t="n">
-        <v>30.8</v>
+        <v>59.4</v>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
@@ -3644,61 +4064,91 @@
         </is>
       </c>
       <c r="W23" s="3" t="n">
-        <v>-8.5</v>
+        <v>45.7</v>
       </c>
       <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC23" s="3" t="inlineStr"/>
-      <c r="AD23" s="3" t="inlineStr"/>
-      <c r="AE23" s="3" t="inlineStr"/>
-      <c r="AF23" s="3" t="inlineStr"/>
-      <c r="AG23" s="3" t="inlineStr"/>
-      <c r="AH23" s="3" t="inlineStr"/>
-      <c r="AI23" s="3" t="inlineStr"/>
-      <c r="AJ23" s="3" t="inlineStr"/>
-      <c r="AK23" s="3" t="inlineStr"/>
-      <c r="AL23" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB23" s="3" t="inlineStr"/>
+      <c r="AC23" s="3" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="AD23" s="3" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="AE23" s="3" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="AF23" s="3" t="n">
+        <v>77.28</v>
+      </c>
+      <c r="AG23" s="3" t="n">
+        <v>71.97200000000001</v>
+      </c>
+      <c r="AH23" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>81.82080000000001</v>
+      </c>
+      <c r="AJ23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>87.54825600000001</v>
+      </c>
+      <c r="AL23" s="3" t="n">
+        <v>15.56</v>
+      </c>
       <c r="AM23" s="3" t="n">
-        <v>210.51</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="AN23" s="3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AO23" s="3" t="inlineStr"/>
-      <c r="AP23" s="3" t="inlineStr"/>
-      <c r="AQ23" s="3" t="inlineStr"/>
+        <v>-0.26</v>
+      </c>
+      <c r="AO23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="inlineStr"/>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU23" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>R2-HD-USA-20260908-2b1b24</t>
+          <t>R1-HOOD-USA-20260908-c0292e</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>HD_USA_20260908</t>
+          <t>HOOD_USA_20260908</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3713,19 +4163,15 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>HD</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Home Depot</t>
-        </is>
-      </c>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3734,27 +4180,37 @@
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>overall breadth 35.7% → -1.0pts · FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>Rank → 13→13 · Conf 35% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 56% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="3" t="n">
-        <v>34.7</v>
+        <v>56.2</v>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
@@ -3762,61 +4218,91 @@
         </is>
       </c>
       <c r="W24" s="3" t="n">
-        <v>-14.6</v>
+        <v>42.9</v>
       </c>
       <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AC24" s="3" t="inlineStr"/>
-      <c r="AD24" s="3" t="inlineStr"/>
-      <c r="AE24" s="3" t="inlineStr"/>
-      <c r="AF24" s="3" t="inlineStr"/>
-      <c r="AG24" s="3" t="inlineStr"/>
-      <c r="AH24" s="3" t="inlineStr"/>
-      <c r="AI24" s="3" t="inlineStr"/>
-      <c r="AJ24" s="3" t="inlineStr"/>
-      <c r="AK24" s="3" t="inlineStr"/>
-      <c r="AL24" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AC24" s="3" t="n">
+        <v>122.11</v>
+      </c>
+      <c r="AD24" s="3" t="n">
+        <v>122.11</v>
+      </c>
+      <c r="AE24" s="3" t="n">
+        <v>119.67</v>
+      </c>
+      <c r="AF24" s="3" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="AG24" s="3" t="n">
+        <v>116.0045</v>
+      </c>
+      <c r="AH24" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>131.8788</v>
+      </c>
+      <c r="AJ24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK24" s="3" t="n">
+        <v>141.110316</v>
+      </c>
+      <c r="AL24" s="3" t="n">
+        <v>15.56</v>
+      </c>
       <c r="AM24" s="3" t="n">
-        <v>318.07</v>
+        <v>124.72</v>
       </c>
       <c r="AN24" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AO24" s="3" t="inlineStr"/>
-      <c r="AP24" s="3" t="inlineStr"/>
-      <c r="AQ24" s="3" t="inlineStr"/>
+        <v>-2.09</v>
+      </c>
+      <c r="AO24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR24" s="3" t="inlineStr"/>
-      <c r="AS24" s="3" t="inlineStr"/>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="inlineStr"/>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU24" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>R2-DIS-USA-20260908-3fb881</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>DIS_USA_20260908</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3836,12 +4322,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Walt Disney</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -3852,10 +4338,10 @@
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>0</v>
@@ -3867,12 +4353,12 @@
       <c r="R25" s="3" t="inlineStr"/>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>Rank → 14→14 · Conf 35% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr"/>
       <c r="U25" s="3" t="n">
-        <v>34.7</v>
+        <v>56.8</v>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
@@ -3880,11 +4366,11 @@
         </is>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-16.4</v>
+        <v>29.2</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>60</v>
@@ -3894,7 +4380,7 @@
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr"/>
@@ -3908,10 +4394,10 @@
       <c r="AK25" s="3" t="inlineStr"/>
       <c r="AL25" s="3" t="inlineStr"/>
       <c r="AM25" s="3" t="n">
-        <v>107.16</v>
+        <v>374.34</v>
       </c>
       <c r="AN25" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.33</v>
       </c>
       <c r="AO25" s="3" t="inlineStr"/>
       <c r="AP25" s="3" t="inlineStr"/>
@@ -3922,19 +4408,19 @@
       <c r="AU25" s="3" t="inlineStr"/>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>R2-MCD-USA-20260908-320601</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MCD_USA_20260908</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3954,12 +4440,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3970,10 +4456,10 @@
       <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>0</v>
@@ -3985,12 +4471,12 @@
       <c r="R26" s="3" t="inlineStr"/>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>Rank → 15→15 · Conf 28% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="3" t="n">
-        <v>28.3</v>
+        <v>53.6</v>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
@@ -3998,11 +4484,11 @@
         </is>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-16.7</v>
+        <v>27.8</v>
       </c>
       <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>60</v>
@@ -4012,7 +4498,7 @@
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr"/>
@@ -4026,10 +4512,10 @@
       <c r="AK26" s="3" t="inlineStr"/>
       <c r="AL26" s="3" t="inlineStr"/>
       <c r="AM26" s="3" t="n">
-        <v>259.63</v>
+        <v>378.75</v>
       </c>
       <c r="AN26" s="3" t="n">
-        <v>-1.52</v>
+        <v>-0.97</v>
       </c>
       <c r="AO26" s="3" t="inlineStr"/>
       <c r="AP26" s="3" t="inlineStr"/>
@@ -4040,12 +4526,1494 @@
       <c r="AU26" s="3" t="inlineStr"/>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 08:43</t>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>R2-NVDA-USA-20260908-4b1ba8</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 3→3 · Conf 47% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB27" s="3" t="inlineStr"/>
+      <c r="AC27" s="3" t="inlineStr"/>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr"/>
+      <c r="AF27" s="3" t="inlineStr"/>
+      <c r="AG27" s="3" t="inlineStr"/>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr"/>
+      <c r="AM27" s="3" t="n">
+        <v>228.45</v>
+      </c>
+      <c r="AN27" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AO27" s="3" t="inlineStr"/>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr"/>
+      <c r="AS27" s="3" t="inlineStr"/>
+      <c r="AT27" s="3" t="inlineStr"/>
+      <c r="AU27" s="3" t="inlineStr"/>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>R2-JPM-USA-20260908-d2beb6</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 4→4 · Conf 50% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AC28" s="3" t="inlineStr"/>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AF28" s="3" t="inlineStr"/>
+      <c r="AG28" s="3" t="inlineStr"/>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr"/>
+      <c r="AM28" s="3" t="n">
+        <v>362.06</v>
+      </c>
+      <c r="AN28" s="3" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr"/>
+      <c r="AS28" s="3" t="inlineStr"/>
+      <c r="AT28" s="3" t="inlineStr"/>
+      <c r="AU28" s="3" t="inlineStr"/>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>R2-HON-USA-20260908-fa8c7f</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>HON_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 5→5 · Conf 50% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA29" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB29" s="3" t="inlineStr"/>
+      <c r="AC29" s="3" t="inlineStr"/>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr"/>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr"/>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr"/>
+      <c r="AM29" s="3" t="n">
+        <v>207.63</v>
+      </c>
+      <c r="AN29" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr"/>
+      <c r="AS29" s="3" t="inlineStr"/>
+      <c r="AT29" s="3" t="inlineStr"/>
+      <c r="AU29" s="3" t="inlineStr"/>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>R2-GS-USA-20260908-3897c3</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>GS_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr"/>
+      <c r="K30" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr"/>
+      <c r="O30" s="3" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr"/>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 6→6 · Conf 51% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA30" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB30" s="3" t="inlineStr"/>
+      <c r="AC30" s="3" t="inlineStr"/>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr"/>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr"/>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr"/>
+      <c r="AM30" s="3" t="n">
+        <v>1037.93</v>
+      </c>
+      <c r="AN30" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AO30" s="3" t="inlineStr"/>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr"/>
+      <c r="AS30" s="3" t="inlineStr"/>
+      <c r="AT30" s="3" t="inlineStr"/>
+      <c r="AU30" s="3" t="inlineStr"/>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>R2-AAPL-USA-20260908-b9beae</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr"/>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 7→7 · Conf 50% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="X31" s="3" t="inlineStr"/>
+      <c r="Y31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB31" s="3" t="inlineStr"/>
+      <c r="AC31" s="3" t="inlineStr"/>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr"/>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr"/>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr"/>
+      <c r="AM31" s="3" t="n">
+        <v>328.21</v>
+      </c>
+      <c r="AN31" s="3" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr"/>
+      <c r="AS31" s="3" t="inlineStr"/>
+      <c r="AT31" s="3" t="inlineStr"/>
+      <c r="AU31" s="3" t="inlineStr"/>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>R2-MSFT-USA-20260908-bf7dcd</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
+      <c r="O32" s="3" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 8→8 · Conf 54% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="X32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB32" s="3" t="inlineStr"/>
+      <c r="AC32" s="3" t="inlineStr"/>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr"/>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr"/>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="n">
+        <v>510.12</v>
+      </c>
+      <c r="AN32" s="3" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="AO32" s="3" t="inlineStr"/>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr"/>
+      <c r="AS32" s="3" t="inlineStr"/>
+      <c r="AT32" s="3" t="inlineStr"/>
+      <c r="AU32" s="3" t="inlineStr"/>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>R2-KO-USA-20260908-391a28</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KO_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 9→9 · Conf 50% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB33" s="3" t="inlineStr"/>
+      <c r="AC33" s="3" t="inlineStr"/>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr"/>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="AN33" s="3" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="AO33" s="3" t="inlineStr"/>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr"/>
+      <c r="AS33" s="3" t="inlineStr"/>
+      <c r="AT33" s="3" t="inlineStr"/>
+      <c r="AU33" s="3" t="inlineStr"/>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>R2-MMM-USA-20260908-b8fa69</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 10→10 · Conf 54% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X34" s="3" t="inlineStr"/>
+      <c r="Y34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA34" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB34" s="3" t="inlineStr"/>
+      <c r="AC34" s="3" t="inlineStr"/>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr"/>
+      <c r="AF34" s="3" t="inlineStr"/>
+      <c r="AG34" s="3" t="inlineStr"/>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr"/>
+      <c r="AM34" s="3" t="n">
+        <v>168.31</v>
+      </c>
+      <c r="AN34" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AO34" s="3" t="inlineStr"/>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr"/>
+      <c r="AS34" s="3" t="inlineStr"/>
+      <c r="AT34" s="3" t="inlineStr"/>
+      <c r="AU34" s="3" t="inlineStr"/>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>R2-INTC-USA-20260908-4d7947</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>INTC_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 11→11 · Conf 29% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA35" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AC35" s="3" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr"/>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr"/>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="3" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="AN35" s="3" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr"/>
+      <c r="AS35" s="3" t="inlineStr"/>
+      <c r="AT35" s="3" t="inlineStr"/>
+      <c r="AU35" s="3" t="inlineStr"/>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>R2-BA-USA-20260908-a3245d</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>BA_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 12→12 · Conf 31% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA36" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB36" s="3" t="inlineStr"/>
+      <c r="AC36" s="3" t="inlineStr"/>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr"/>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr"/>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr"/>
+      <c r="AM36" s="3" t="n">
+        <v>210.51</v>
+      </c>
+      <c r="AN36" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr"/>
+      <c r="AS36" s="3" t="inlineStr"/>
+      <c r="AT36" s="3" t="inlineStr"/>
+      <c r="AU36" s="3" t="inlineStr"/>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>R2-HD-USA-20260908-2b1b24</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>HD_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 13→13 · Conf 35% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr"/>
+      <c r="Y37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA37" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB37" s="3" t="inlineStr"/>
+      <c r="AC37" s="3" t="inlineStr"/>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr"/>
+      <c r="AF37" s="3" t="inlineStr"/>
+      <c r="AG37" s="3" t="inlineStr"/>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr"/>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr"/>
+      <c r="AM37" s="3" t="n">
+        <v>318.07</v>
+      </c>
+      <c r="AN37" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AO37" s="3" t="inlineStr"/>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr"/>
+      <c r="AS37" s="3" t="inlineStr"/>
+      <c r="AT37" s="3" t="inlineStr"/>
+      <c r="AU37" s="3" t="inlineStr"/>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>R2-DIS-USA-20260908-3fb881</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>DIS_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="inlineStr"/>
+      <c r="P38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 14→14 · Conf 35% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="X38" s="3" t="inlineStr"/>
+      <c r="Y38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA38" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB38" s="3" t="inlineStr"/>
+      <c r="AC38" s="3" t="inlineStr"/>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr"/>
+      <c r="AF38" s="3" t="inlineStr"/>
+      <c r="AG38" s="3" t="inlineStr"/>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr"/>
+      <c r="AM38" s="3" t="n">
+        <v>107.16</v>
+      </c>
+      <c r="AN38" s="3" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="AO38" s="3" t="inlineStr"/>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr"/>
+      <c r="AS38" s="3" t="inlineStr"/>
+      <c r="AT38" s="3" t="inlineStr"/>
+      <c r="AU38" s="3" t="inlineStr"/>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>R2-MCD-USA-20260908-320601</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>MCD_USA_20260908</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr"/>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr"/>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>Rank → 15→15 · Conf 28% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="X39" s="3" t="inlineStr"/>
+      <c r="Y39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA39" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB39" s="3" t="inlineStr"/>
+      <c r="AC39" s="3" t="inlineStr"/>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr"/>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr"/>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr"/>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr"/>
+      <c r="AM39" s="3" t="n">
+        <v>259.63</v>
+      </c>
+      <c r="AN39" s="3" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr"/>
+      <c r="AS39" s="3" t="inlineStr"/>
+      <c r="AT39" s="3" t="inlineStr"/>
+      <c r="AU39" s="3" t="inlineStr"/>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:34</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV26"/>
+  <autoFilter ref="A1:AV39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-09-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-08.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -1032,11 +1032,11 @@
       <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -1186,11 +1186,11 @@
       <c r="AS4" s="3" t="inlineStr"/>
       <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -1340,11 +1340,11 @@
       <c r="AS5" s="3" t="inlineStr"/>
       <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>6.49</v>
+        <v>6.52</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -1494,11 +1494,11 @@
       <c r="AS6" s="3" t="inlineStr"/>
       <c r="AT6" s="3" t="inlineStr"/>
       <c r="AU6" s="3" t="n">
-        <v>7.03</v>
+        <v>7.04</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>1</v>
@@ -1648,11 +1648,11 @@
       <c r="AS7" s="3" t="inlineStr"/>
       <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -1802,11 +1802,11 @@
       <c r="AS8" s="3" t="inlineStr"/>
       <c r="AT8" s="3" t="inlineStr"/>
       <c r="AU8" s="3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -1960,11 +1960,11 @@
       <c r="AS9" s="3" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -2114,11 +2114,11 @@
       <c r="AS10" s="3" t="inlineStr"/>
       <c r="AT10" s="3" t="inlineStr"/>
       <c r="AU10" s="3" t="n">
-        <v>61.27</v>
+        <v>61.29</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -2268,11 +2268,11 @@
       <c r="AS11" s="3" t="inlineStr"/>
       <c r="AT11" s="3" t="inlineStr"/>
       <c r="AU11" s="3" t="n">
-        <v>62.63</v>
+        <v>62.65</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -2426,11 +2426,11 @@
       <c r="AS12" s="3" t="inlineStr"/>
       <c r="AT12" s="3" t="inlineStr"/>
       <c r="AU12" s="3" t="n">
-        <v>62.69</v>
+        <v>62.72</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>→ SMCI · +63.6pp alpha</t>
+          <t>→ SMCI · +63.7pp alpha</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
@@ -2584,11 +2584,11 @@
       <c r="AS13" s="3" t="inlineStr"/>
       <c r="AT13" s="3" t="inlineStr"/>
       <c r="AU13" s="3" t="n">
-        <v>63.63</v>
+        <v>63.66</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -2742,11 +2742,11 @@
       <c r="AS14" s="3" t="inlineStr"/>
       <c r="AT14" s="3" t="inlineStr"/>
       <c r="AU14" s="3" t="n">
-        <v>66.70999999999999</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       <c r="AU25" s="3" t="inlineStr"/>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       <c r="AU26" s="3" t="inlineStr"/>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       <c r="AU27" s="3" t="inlineStr"/>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       <c r="AU28" s="3" t="inlineStr"/>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       <c r="AU29" s="3" t="inlineStr"/>
       <c r="AV29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -4982,7 +4982,7 @@
       <c r="AU30" s="3" t="inlineStr"/>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       <c r="AU31" s="3" t="inlineStr"/>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       <c r="AU32" s="3" t="inlineStr"/>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       <c r="AU33" s="3" t="inlineStr"/>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       <c r="AU34" s="3" t="inlineStr"/>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       <c r="AU35" s="3" t="inlineStr"/>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       <c r="AU36" s="3" t="inlineStr"/>
       <c r="AV36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       <c r="AU37" s="3" t="inlineStr"/>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       <c r="AU38" s="3" t="inlineStr"/>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       <c r="AU39" s="3" t="inlineStr"/>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 12:34</t>
+          <t>2026-09-08 13:09</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-09-08.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-08.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -1032,11 +1032,11 @@
       <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>5.91</v>
+        <v>5.92</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -1186,11 +1186,11 @@
       <c r="AS4" s="3" t="inlineStr"/>
       <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
-        <v>6.4</v>
+        <v>6.38</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -1340,11 +1340,11 @@
       <c r="AS5" s="3" t="inlineStr"/>
       <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -1498,19 +1498,19 @@
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R2-SNDK-USA-20260908-6245dc</t>
+          <t>R2-GRMN-USA-20260908-8a1473</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SNDK_USA_20260908</t>
+          <t>GRMN_USA_20260908</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="n">
-        <v>74.8</v>
+        <v>72</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>-1.8</v>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #8 · Conf 50% · band HOLD · 9d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #8 · Conf 59% · band HOLD · 17d left · → HOLD</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>49.9</v>
+        <v>59.1</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>1</v>
@@ -1589,47 +1589,47 @@
         <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>1740</v>
+        <v>277.03</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>1740</v>
+        <v>277.03</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1722.6</v>
+        <v>274.26</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>1757.4</v>
+        <v>279.8</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>1653</v>
+        <v>263.18</v>
       </c>
       <c r="AH7" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>1879.2</v>
+        <v>299.19</v>
       </c>
       <c r="AJ7" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>2001</v>
+        <v>318.58</v>
       </c>
       <c r="AL7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>1554.99</v>
+        <v>277.18</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>11.9</v>
+        <v>-0.05</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>0</v>
@@ -1642,29 +1642,29 @@
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Quality · Mean Reversion · Momentum</t>
+          <t>Mean Reversion · Quality · News</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr"/>
       <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="n">
-        <v>8.550000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R2-GRMN-USA-20260908-8a1473</t>
+          <t>R2-SNDK-USA-20260908-6245dc</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>GRMN_USA_20260908</t>
+          <t>SNDK_USA_20260908</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="n">
-        <v>72</v>
+        <v>74.8</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>57.3</v>
+        <v>48.1</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>-1.8</v>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 59% · band HOLD · 17d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 50% · band HOLD · 9d left · → HOLD</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>59.1</v>
+        <v>49.9</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1743,47 +1743,47 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AA8" s="3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>277.03</v>
+        <v>1740</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>277.03</v>
+        <v>1740</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>274.26</v>
+        <v>1722.6</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>279.8</v>
+        <v>1757.4</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>263.18</v>
+        <v>1653</v>
       </c>
       <c r="AH8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>299.19</v>
+        <v>1879.2</v>
       </c>
       <c r="AJ8" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>318.58</v>
+        <v>2001</v>
       </c>
       <c r="AL8" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>277.18</v>
+        <v>1554.99</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-0.05</v>
+        <v>11.9</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>0</v>
@@ -1796,17 +1796,17 @@
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Mean Reversion · Quality · News</t>
+          <t>Quality · Mean Reversion · Momentum</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr"/>
       <c r="AT8" s="3" t="inlineStr"/>
       <c r="AU8" s="3" t="n">
-        <v>8.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -1960,11 +1960,11 @@
       <c r="AS9" s="3" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="n">
-        <v>9.49</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -2114,11 +2114,11 @@
       <c r="AS10" s="3" t="inlineStr"/>
       <c r="AT10" s="3" t="inlineStr"/>
       <c r="AU10" s="3" t="n">
-        <v>61.29</v>
+        <v>61.28</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -2268,11 +2268,11 @@
       <c r="AS11" s="3" t="inlineStr"/>
       <c r="AT11" s="3" t="inlineStr"/>
       <c r="AU11" s="3" t="n">
-        <v>62.65</v>
+        <v>62.63</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -2426,11 +2426,11 @@
       <c r="AS12" s="3" t="inlineStr"/>
       <c r="AT12" s="3" t="inlineStr"/>
       <c r="AU12" s="3" t="n">
-        <v>62.72</v>
+        <v>62.7</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>→ SMCI · +63.7pp alpha</t>
+          <t>→ SMCI · +63.6pp alpha</t>
         </is>
       </c>
       <c r="J13" s="3" t="n">
@@ -2584,11 +2584,11 @@
       <c r="AS13" s="3" t="inlineStr"/>
       <c r="AT13" s="3" t="inlineStr"/>
       <c r="AU13" s="3" t="n">
-        <v>63.66</v>
+        <v>63.64</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -2742,11 +2742,11 @@
       <c r="AS14" s="3" t="inlineStr"/>
       <c r="AT14" s="3" t="inlineStr"/>
       <c r="AU14" s="3" t="n">
-        <v>66.73999999999999</v>
+        <v>66.72</v>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       <c r="AU25" s="3" t="inlineStr"/>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       <c r="AU26" s="3" t="inlineStr"/>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       <c r="AU27" s="3" t="inlineStr"/>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       <c r="AU28" s="3" t="inlineStr"/>
       <c r="AV28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       <c r="AU29" s="3" t="inlineStr"/>
       <c r="AV29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -4982,7 +4982,7 @@
       <c r="AU30" s="3" t="inlineStr"/>
       <c r="AV30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       <c r="AU31" s="3" t="inlineStr"/>
       <c r="AV31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       <c r="AU32" s="3" t="inlineStr"/>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       <c r="AU33" s="3" t="inlineStr"/>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       <c r="AU34" s="3" t="inlineStr"/>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       <c r="AU35" s="3" t="inlineStr"/>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       <c r="AU36" s="3" t="inlineStr"/>
       <c r="AV36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       <c r="AU37" s="3" t="inlineStr"/>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       <c r="AU38" s="3" t="inlineStr"/>
       <c r="AV38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       <c r="AU39" s="3" t="inlineStr"/>
       <c r="AV39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:09</t>
+          <t>2026-09-08 13:29</t>
         </is>
       </c>
     </row>
